--- a/vman_ml/resources/va_instr_2016.xlsx
+++ b/vman_ml/resources/va_instr_2016.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilyatuu/Documents/Projects/MOH/CRVS_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ilyatuu/Documents/Code/vman3/vman_ml/vman_ml/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6903C128-A0E5-1447-AB82-E19A7ED48ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130448DD-C942-7D4A-AE74-21B83E186B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="3100" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12100" yWindow="660" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet name="mapping" sheetId="4" r:id="rId3"/>
+    <sheet name="settings" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_2016survey">survey!$A$1:$P$552</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="4178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11558" uniqueCount="4573">
   <si>
     <t>type</t>
   </si>
@@ -12837,12 +12838,1197 @@
   <si>
     <t xml:space="preserve">Hakuajiriwa </t>
   </si>
+  <si>
+    <t>GENERAL VARIABLES (Applies to All Age Groups)</t>
+  </si>
+  <si>
+    <t>Variable 2016</t>
+  </si>
+  <si>
+    <t>Label 2016</t>
+  </si>
+  <si>
+    <t>Variable 2022</t>
+  </si>
+  <si>
+    <t>Label 2022</t>
+  </si>
+  <si>
+    <t>Intro Section</t>
+  </si>
+  <si>
+    <t>Start time of interview</t>
+  </si>
+  <si>
+    <t>End time of interview</t>
+  </si>
+  <si>
+    <t>Today's date</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>Interviewer Information</t>
+  </si>
+  <si>
+    <t>Name of VA interviewer</t>
+  </si>
+  <si>
+    <t>Age of VA interviewer</t>
+  </si>
+  <si>
+    <t>Sex of VA interviewer</t>
+  </si>
+  <si>
+    <t>ID of VA interviewer</t>
+  </si>
+  <si>
+    <t>Presets</t>
+  </si>
+  <si>
+    <t>Is this a region of high HIV/AIDS mortality?</t>
+  </si>
+  <si>
+    <t>Is this a region of high malaria mortality?</t>
+  </si>
+  <si>
+    <t>During which season did (s)he die?</t>
+  </si>
+  <si>
+    <t>Respondent Information</t>
+  </si>
+  <si>
+    <t>Full name of VA respondent</t>
+  </si>
+  <si>
+    <t>Sex of VA respondent</t>
+  </si>
+  <si>
+    <t>Age of VA respondent</t>
+  </si>
+  <si>
+    <t>Phone number for VA respondent</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Not present in 2022</t>
+  </si>
+  <si>
+    <t>Respondent's relationship to deceased</t>
+  </si>
+  <si>
+    <t>Did respondent live with deceased in period leading to death?</t>
+  </si>
+  <si>
+    <t>Date of interview</t>
+  </si>
+  <si>
+    <t>Region where interview is happening</t>
+  </si>
+  <si>
+    <t>District where interview is happening</t>
+  </si>
+  <si>
+    <t>Other District</t>
+  </si>
+  <si>
+    <t>Ward where interview is happening</t>
+  </si>
+  <si>
+    <t>Shehia where interview is happening</t>
+  </si>
+  <si>
+    <t>Village or street where interview is happening</t>
+  </si>
+  <si>
+    <t>Did respondent give consent?</t>
+  </si>
+  <si>
+    <t>DECEASED INFORMATION</t>
+  </si>
+  <si>
+    <t>First/given name(s) of deceased</t>
+  </si>
+  <si>
+    <t>Surname(s)/family name(s) of deceased</t>
+  </si>
+  <si>
+    <t>Sex of deceased</t>
+  </si>
+  <si>
+    <t>Is date of birth known?</t>
+  </si>
+  <si>
+    <t>When was deceased born?</t>
+  </si>
+  <si>
+    <t>Is date of death known?</t>
+  </si>
+  <si>
+    <t>When did (s)he die? (with DOB)</t>
+  </si>
+  <si>
+    <t>When did (s)he die? (without DOB)</t>
+  </si>
+  <si>
+    <t>When did (s)he die? (calculated)</t>
+  </si>
+  <si>
+    <t>Year of death</t>
+  </si>
+  <si>
+    <t>Age in years</t>
+  </si>
+  <si>
+    <t>Age in months</t>
+  </si>
+  <si>
+    <t>Deceased is a neonate</t>
+  </si>
+  <si>
+    <t>Deceased is a child</t>
+  </si>
+  <si>
+    <t>Deceased is an adult</t>
+  </si>
+  <si>
+    <t>Age group of deceased</t>
+  </si>
+  <si>
+    <t>Neonate age in days</t>
+  </si>
+  <si>
+    <t>Neonate age in hours</t>
+  </si>
+  <si>
+    <t>Child age unit</t>
+  </si>
+  <si>
+    <t>Child age in days</t>
+  </si>
+  <si>
+    <t>Child age in months</t>
+  </si>
+  <si>
+    <t>Child age in years</t>
+  </si>
+  <si>
+    <t>Adult age in years</t>
+  </si>
+  <si>
+    <t>Where did deceased die?</t>
+  </si>
+  <si>
+    <t>Other place of death</t>
+  </si>
+  <si>
+    <t>DEMOGRAPHIC &amp; SOCIOECONOMIC DATA</t>
+  </si>
+  <si>
+    <t>Collect additional demographic data?</t>
+  </si>
+  <si>
+    <t>Citizenship/nationality</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Id10054</t>
+  </si>
+  <si>
+    <t>Place of birth</t>
+  </si>
+  <si>
+    <t>Part of Id10054</t>
+  </si>
+  <si>
+    <t>Shehia of birth</t>
+  </si>
+  <si>
+    <t>Place of usual residence</t>
+  </si>
+  <si>
+    <t>Where did death occur?</t>
+  </si>
+  <si>
+    <t>Region of death</t>
+  </si>
+  <si>
+    <t>Part of Id10057</t>
+  </si>
+  <si>
+    <t>District of death</t>
+  </si>
+  <si>
+    <t>Shehia of death</t>
+  </si>
+  <si>
+    <t>Village of death</t>
+  </si>
+  <si>
+    <t>Place if death outside country</t>
+  </si>
+  <si>
+    <t>Marital status</t>
+  </si>
+  <si>
+    <t>Highest level of schooling</t>
+  </si>
+  <si>
+    <t>Able to read and/or write?</t>
+  </si>
+  <si>
+    <t>Economic activity status</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Full name of father</t>
+  </si>
+  <si>
+    <t>Full name of mother</t>
+  </si>
+  <si>
+    <t>NARRATIVE &amp; CIVIL REGISTRATION</t>
+  </si>
+  <si>
+    <t>Audio recording of narrative</t>
+  </si>
+  <si>
+    <t>Open narrative text</t>
+  </si>
+  <si>
+    <t>Key words (adult narrative)</t>
+  </si>
+  <si>
+    <t>Key words (child narrative)</t>
+  </si>
+  <si>
+    <t>Key words (neonate narrative)</t>
+  </si>
+  <si>
+    <t>Death Certificate from Civil Registry?</t>
+  </si>
+  <si>
+    <t>Death registration number/certificate</t>
+  </si>
+  <si>
+    <t>Date of registration available?</t>
+  </si>
+  <si>
+    <t>Date of registration</t>
+  </si>
+  <si>
+    <t>Place of registration</t>
+  </si>
+  <si>
+    <t>National identification number</t>
+  </si>
+  <si>
+    <t>Did deceased have Health Insurance?</t>
+  </si>
+  <si>
+    <t>Which Health Insurance?</t>
+  </si>
+  <si>
+    <t>Did deceased use Health Insurance?</t>
+  </si>
+  <si>
+    <t>Which services did Insurance provide?</t>
+  </si>
+  <si>
+    <t>Why did deceased not use insurance?</t>
+  </si>
+  <si>
+    <t>MEDICAL CERTIFICATE OF DEATH</t>
+  </si>
+  <si>
+    <t>Was medical certificate of cause of death issued?</t>
+  </si>
+  <si>
+    <t>Can I see the medical certificate?</t>
+  </si>
+  <si>
+    <t>Immediate cause of death (1a)</t>
+  </si>
+  <si>
+    <t>Duration of immediate cause (1a)</t>
+  </si>
+  <si>
+    <t>First antecedent cause (1b)</t>
+  </si>
+  <si>
+    <t>Duration of first antecedent (1b)</t>
+  </si>
+  <si>
+    <t>Second antecedent cause (1c)</t>
+  </si>
+  <si>
+    <t>Duration of second antecedent (1c)</t>
+  </si>
+  <si>
+    <t>Third antecedent cause (1d)</t>
+  </si>
+  <si>
+    <t>Duration of third antecedent (1d)</t>
+  </si>
+  <si>
+    <t>Contributing causes (part 2)</t>
+  </si>
+  <si>
+    <t>Duration of contributing causes</t>
+  </si>
+  <si>
+    <t>STILLBIRTH / NEONATAL BIRTH VARIABLES (Neonates Only)</t>
+  </si>
+  <si>
+    <t>Did the baby ever cry?</t>
+  </si>
+  <si>
+    <t>Did the baby cry immediately after birth?</t>
+  </si>
+  <si>
+    <t>How many minutes after birth did baby first cry?</t>
+  </si>
+  <si>
+    <t>Did the baby stop being able to cry?</t>
+  </si>
+  <si>
+    <t>Did the baby stop moving in the womb?</t>
+  </si>
+  <si>
+    <t>Did baby stop moving before or after labour onset?</t>
+  </si>
+  <si>
+    <t>Did the baby ever move after being delivered?</t>
+  </si>
+  <si>
+    <t>Did the baby ever breathe?</t>
+  </si>
+  <si>
+    <t>Did the baby breathe immediately after birth?</t>
+  </si>
+  <si>
+    <t>Did the baby have a breathing problem?</t>
+  </si>
+  <si>
+    <t>Was baby given assistance to breathe at birth?</t>
+  </si>
+  <si>
+    <t>If baby didn't show signs of life, was it born dead?</t>
+  </si>
+  <si>
+    <t>Were there bruises or signs of injury after birth?</t>
+  </si>
+  <si>
+    <t>Was baby's body soft, discoloured and skin peeling?</t>
+  </si>
+  <si>
+    <t>How many days old when fatal illness started?</t>
+  </si>
+  <si>
+    <t>Before illness, was baby/child growing normally?</t>
+  </si>
+  <si>
+    <t>Was child part of a multiple birth?</t>
+  </si>
+  <si>
+    <t>Is child health card available?</t>
+  </si>
+  <si>
+    <t>Weight at birth (grammes)</t>
+  </si>
+  <si>
+    <t>At birth, was baby smaller than usual (&lt;2.5 kg)?</t>
+  </si>
+  <si>
+    <t>At birth, was baby larger than usual (&gt;4.5 kg)?</t>
+  </si>
+  <si>
+    <t>How many months was pregnancy?</t>
+  </si>
+  <si>
+    <t>Were there complications during labour/delivery?</t>
+  </si>
+  <si>
+    <t>Was any part of baby physically abnormal at birth?</t>
+  </si>
+  <si>
+    <t>Did baby have swelling or defect on back?</t>
+  </si>
+  <si>
+    <t>Did baby have a very large head at birth?</t>
+  </si>
+  <si>
+    <t>Did baby have a very small head at birth?</t>
+  </si>
+  <si>
+    <t>How many hours did labour and delivery take?</t>
+  </si>
+  <si>
+    <t>Was baby born 24+ hours after water broke?</t>
+  </si>
+  <si>
+    <t>Was the liquor foul smelling?</t>
+  </si>
+  <si>
+    <t>What was the colour of the liquor?</t>
+  </si>
+  <si>
+    <t>Was delivery normal vaginal?</t>
+  </si>
+  <si>
+    <t>Was delivery vaginal with forceps/vacuum?</t>
+  </si>
+  <si>
+    <t>Was delivery a Caesarean section?</t>
+  </si>
+  <si>
+    <t>Did mother receive vaccinations since adulthood?</t>
+  </si>
+  <si>
+    <t>Did mother receive tetanus toxoid vaccine?</t>
+  </si>
+  <si>
+    <t>During labour, did mother suffer from fever?</t>
+  </si>
+  <si>
+    <t>During pregnancy/labour, did mother have high BP?</t>
+  </si>
+  <si>
+    <t>Did mother have diabetes mellitus?</t>
+  </si>
+  <si>
+    <t>Did mother have foul vaginal discharge during pregnancy?</t>
+  </si>
+  <si>
+    <t>Did mother suffer from convulsions?</t>
+  </si>
+  <si>
+    <t>Did mother suffer from blurred vision?</t>
+  </si>
+  <si>
+    <t>Did mother have severe anaemia?</t>
+  </si>
+  <si>
+    <t>Did mother have vaginal bleeding in last 3 months?</t>
+  </si>
+  <si>
+    <t>Did baby's bottom/feet come out before head?</t>
+  </si>
+  <si>
+    <t>Was umbilical cord wrapped &gt; once around neck?</t>
+  </si>
+  <si>
+    <t>Was umbilical cord delivered first?</t>
+  </si>
+  <si>
+    <t>Was baby blue in colour at birth?</t>
+  </si>
+  <si>
+    <t>Has mother ever been told she had HIV/AIDS?</t>
+  </si>
+  <si>
+    <t>Was baby able to suckle within first 24 hours?</t>
+  </si>
+  <si>
+    <t>Did the baby ever suckle in a normal way?</t>
+  </si>
+  <si>
+    <t>Did the baby stop suckling?</t>
+  </si>
+  <si>
+    <t>How many days after birth did baby stop suckling?</t>
+  </si>
+  <si>
+    <t>How long after birth did baby stop suckling?</t>
+  </si>
+  <si>
+    <t>Days after birth baby stopped suckling</t>
+  </si>
+  <si>
+    <t>Months after birth baby stopped suckling</t>
+  </si>
+  <si>
+    <t>Calculated days after birth baby stopped suckling</t>
+  </si>
+  <si>
+    <t>Did baby's body become stiff with arched back?</t>
+  </si>
+  <si>
+    <t>Did baby have bulging fontanelle?</t>
+  </si>
+  <si>
+    <t>Did baby have sunken fontanelle?</t>
+  </si>
+  <si>
+    <t>Did baby become unresponsive or unconscious?</t>
+  </si>
+  <si>
+    <t>Did baby become unresponsive within 24 hours?</t>
+  </si>
+  <si>
+    <t>Did baby become unresponsive after 24 hours?</t>
+  </si>
+  <si>
+    <t>Did baby become cold to touch?</t>
+  </si>
+  <si>
+    <t>Did baby become lethargic after normal activity?</t>
+  </si>
+  <si>
+    <t>Did baby have redness/pus from umbilical cord?</t>
+  </si>
+  <si>
+    <t>Did baby have skin ulcers or sores?</t>
+  </si>
+  <si>
+    <t>Did baby have yellow skin, palms or soles?</t>
+  </si>
+  <si>
+    <t>Did baby have convulsions within first 24 hours?</t>
+  </si>
+  <si>
+    <t>Did baby have convulsions after 24 hours?</t>
+  </si>
+  <si>
+    <t>Did baby have areas of skin that turned black?</t>
+  </si>
+  <si>
+    <t>Did baby have areas of skin with redness/swelling?</t>
+  </si>
+  <si>
+    <t>INJURIES &amp; ACCIDENTS (All Age Groups)</t>
+  </si>
+  <si>
+    <t>Did (s)he suffer from injury/accident leading to death?</t>
+  </si>
+  <si>
+    <t>How long after injury/accident did (s)he die?</t>
+  </si>
+  <si>
+    <t>Confirm death within 7 days of accident</t>
+  </si>
+  <si>
+    <t>Was it a road transport injury?</t>
+  </si>
+  <si>
+    <t>Was it a non-road transport injury?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured in a fall?</t>
+  </si>
+  <si>
+    <t>Was there any poisoning?</t>
+  </si>
+  <si>
+    <t>Did (s)he die of drowning?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by venomous bite/sting?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by non-venomous animal/insect?</t>
+  </si>
+  <si>
+    <t>What was the animal/insect?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by burns/fire?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by a firearm?</t>
+  </si>
+  <si>
+    <t>Was (s)he stabbed, cut or pierced?</t>
+  </si>
+  <si>
+    <t>Was (s)he strangled?</t>
+  </si>
+  <si>
+    <t>Was (s)he electrocuted?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by a blunt force?</t>
+  </si>
+  <si>
+    <t>Was (s)he injured by a force of nature?</t>
+  </si>
+  <si>
+    <t>Did (s)he suffer any other injury?</t>
+  </si>
+  <si>
+    <t>Was the injury accidental?</t>
+  </si>
+  <si>
+    <t>Was the injury self-inflicted?</t>
+  </si>
+  <si>
+    <t>Was the injury intentionally inflicted by someone else?</t>
+  </si>
+  <si>
+    <t>DURATION OF ILLNESS &amp; GENERAL SYMPTOMS (All Age Groups)</t>
+  </si>
+  <si>
+    <t>Days ill before death (neonate)</t>
+  </si>
+  <si>
+    <t>Id10120_unit</t>
+  </si>
+  <si>
+    <t>Duration of illness unit</t>
+  </si>
+  <si>
+    <t>Duration in months</t>
+  </si>
+  <si>
+    <t>Duration in years</t>
+  </si>
+  <si>
+    <t>Duration in days</t>
+  </si>
+  <si>
+    <t>Calculated duration in days</t>
+  </si>
+  <si>
+    <t>Did (s)he die suddenly?</t>
+  </si>
+  <si>
+    <t>SYMPTOMS &amp; CONDITIONS (Adult &amp; Child)</t>
+  </si>
+  <si>
+    <t>Diagnosed Conditions</t>
+  </si>
+  <si>
+    <t>Diagnosis of tuberculosis</t>
+  </si>
+  <si>
+    <t>HIV test ever positive</t>
+  </si>
+  <si>
+    <t>Diagnosis of AIDS</t>
+  </si>
+  <si>
+    <t>Recent positive test for malaria</t>
+  </si>
+  <si>
+    <t>Recent negative test for malaria</t>
+  </si>
+  <si>
+    <t>Diagnosis of COVID-19</t>
+  </si>
+  <si>
+    <t>Recent test for COVID-19</t>
+  </si>
+  <si>
+    <t>COVID-19 test result</t>
+  </si>
+  <si>
+    <t>Diagnosis of dengue fever</t>
+  </si>
+  <si>
+    <t>Diagnosis of measles</t>
+  </si>
+  <si>
+    <t>Diagnosis of high blood pressure</t>
+  </si>
+  <si>
+    <t>Diagnosis of heart disease</t>
+  </si>
+  <si>
+    <t>Diagnosis of diabetes</t>
+  </si>
+  <si>
+    <t>Diagnosis of asthma</t>
+  </si>
+  <si>
+    <t>Diagnosis of epilepsy</t>
+  </si>
+  <si>
+    <t>Diagnosis of cancer</t>
+  </si>
+  <si>
+    <t>Diagnosis of COPD</t>
+  </si>
+  <si>
+    <t>Diagnosis of dementia</t>
+  </si>
+  <si>
+    <t>Diagnosis of depression</t>
+  </si>
+  <si>
+    <t>Diagnosis of stroke</t>
+  </si>
+  <si>
+    <t>Diagnosis of sickle cell disease</t>
+  </si>
+  <si>
+    <t>Diagnosis of kidney disease</t>
+  </si>
+  <si>
+    <t>Diagnosis of liver disease</t>
+  </si>
+  <si>
+    <t>Fever Symptoms</t>
+  </si>
+  <si>
+    <t>Did (s)he have a fever?</t>
+  </si>
+  <si>
+    <t>How many days did fever last? (neonate)</t>
+  </si>
+  <si>
+    <t>Duration of fever unit</t>
+  </si>
+  <si>
+    <t>Duration of fever in days</t>
+  </si>
+  <si>
+    <t>Duration of fever in months</t>
+  </si>
+  <si>
+    <t>Calculated duration of fever</t>
+  </si>
+  <si>
+    <t>Did fever continue until death?</t>
+  </si>
+  <si>
+    <t>How severe was the fever?</t>
+  </si>
+  <si>
+    <t>What was the pattern of fever?</t>
+  </si>
+  <si>
+    <t>Cough Symptoms</t>
+  </si>
+  <si>
+    <t>Did (s)he have a cough?</t>
+  </si>
+  <si>
+    <t>Duration of cough unit</t>
+  </si>
+  <si>
+    <t>Duration of cough in days</t>
+  </si>
+  <si>
+    <t>Duration of cough in months</t>
+  </si>
+  <si>
+    <t>Calculated duration of cough</t>
+  </si>
+  <si>
+    <t>Was cough productive with sputum?</t>
+  </si>
+  <si>
+    <t>Was the cough very severe?</t>
+  </si>
+  <si>
+    <t>Did (s)he cough up blood?</t>
+  </si>
+  <si>
+    <t>Did (s)he make a whooping sound when coughing?</t>
+  </si>
+  <si>
+    <t>Breathing Symptoms</t>
+  </si>
+  <si>
+    <t>Did (s)he have difficulty breathing/breathlessness?</t>
+  </si>
+  <si>
+    <t>Duration of breathing difficulty (neonate)</t>
+  </si>
+  <si>
+    <t>Id10161_unit</t>
+  </si>
+  <si>
+    <t>Duration of breathing difficulty unit</t>
+  </si>
+  <si>
+    <t>Calculated duration</t>
+  </si>
+  <si>
+    <t>Was breathing difficulty continuous or on/off?</t>
+  </si>
+  <si>
+    <t>Unable to carry out daily routines due to breathlessness?</t>
+  </si>
+  <si>
+    <t>Breathless while lying flat?</t>
+  </si>
+  <si>
+    <t>Did (s)he have fast breathing?</t>
+  </si>
+  <si>
+    <t>Duration of fast breathing (neonate)</t>
+  </si>
+  <si>
+    <t>Duration of fast breathing unit</t>
+  </si>
+  <si>
+    <t>Did you see chest in-drawing?</t>
+  </si>
+  <si>
+    <t>Breathing sounds (neonate/child)</t>
+  </si>
+  <si>
+    <t>Wheezing (adult)</t>
+  </si>
+  <si>
+    <t>Breathing sounds (calculated)</t>
+  </si>
+  <si>
+    <t>Chest Pain</t>
+  </si>
+  <si>
+    <t>Did (s)he have chest pain?</t>
+  </si>
+  <si>
+    <t>Was chest pain severe?</t>
+  </si>
+  <si>
+    <t>How many days before death did chest pain occur?</t>
+  </si>
+  <si>
+    <t>Duration of chest pain unit</t>
+  </si>
+  <si>
+    <t>Duration in hours</t>
+  </si>
+  <si>
+    <t>Gastrointestinal Symptoms</t>
+  </si>
+  <si>
+    <t>Did (s)he have diarrhoea?</t>
+  </si>
+  <si>
+    <t>Duration of diarrhoea unit</t>
+  </si>
+  <si>
+    <t>How many stools on most frequent day?</t>
+  </si>
+  <si>
+    <t>Days before death diarrhoea started (neonate)</t>
+  </si>
+  <si>
+    <t>Time before death diarrhoea started unit</t>
+  </si>
+  <si>
+    <t>Time in days</t>
+  </si>
+  <si>
+    <t>Time in months</t>
+  </si>
+  <si>
+    <t>Did diarrhoea continue until death?</t>
+  </si>
+  <si>
+    <t>Was there blood in stools?</t>
+  </si>
+  <si>
+    <t>Did (s)he vomit?</t>
+  </si>
+  <si>
+    <t>Duration of vomiting unit</t>
+  </si>
+  <si>
+    <t>Did (s)he vomit in week preceding death?</t>
+  </si>
+  <si>
+    <t>Did (s)he vomit every time ate/drank?</t>
+  </si>
+  <si>
+    <t>Was there blood in vomit?</t>
+  </si>
+  <si>
+    <t>Was the vomit black?</t>
+  </si>
+  <si>
+    <t>Abdominal Symptoms</t>
+  </si>
+  <si>
+    <t>Did (s)he have abdominal pain?</t>
+  </si>
+  <si>
+    <t>Was abdominal pain severe?</t>
+  </si>
+  <si>
+    <t>Id10196_unit</t>
+  </si>
+  <si>
+    <t>Duration of abdominal pain unit</t>
+  </si>
+  <si>
+    <t>Location of abdominal pain</t>
+  </si>
+  <si>
+    <t>Did (s)he have protruding abdomen?</t>
+  </si>
+  <si>
+    <t>Duration of protruding abdomen unit</t>
+  </si>
+  <si>
+    <t>How rapidly did protruding abdomen develop?</t>
+  </si>
+  <si>
+    <t>Did (s)he have abdominal mass?</t>
+  </si>
+  <si>
+    <t>FEMALE-ONLY VARIABLES (Pregnancy &amp; Maternal Health)</t>
+  </si>
+  <si>
+    <t>Breast &amp; Reproductive History</t>
+  </si>
+  <si>
+    <t>Did she have any lump(s) and/or ulcer(s) in the breast?</t>
+  </si>
+  <si>
+    <t>Did she ever have a period or menstruate?</t>
+  </si>
+  <si>
+    <t>Did her menstrual period stop naturally because of menopause?</t>
+  </si>
+  <si>
+    <t>Did she have vaginal bleeding after cessation of menstruation?</t>
+  </si>
+  <si>
+    <t>Was there excessive vaginal bleeding in the week prior to death?</t>
+  </si>
+  <si>
+    <t>At the time of death was her period overdue?</t>
+  </si>
+  <si>
+    <t>For how many weeks had her period been overdue?</t>
+  </si>
+  <si>
+    <t>Pregnancy Status</t>
+  </si>
+  <si>
+    <t>Was she pregnant and not yet in labour at the time of death?</t>
+  </si>
+  <si>
+    <t>Did she die during labour or delivery?</t>
+  </si>
+  <si>
+    <t>Did she die after delivering a baby?</t>
+  </si>
+  <si>
+    <t>Did she die within 24 hours after delivery?</t>
+  </si>
+  <si>
+    <t>Did she die within 6 weeks after delivery?</t>
+  </si>
+  <si>
+    <t>Did she have a pregnancy that ended in abortion or miscarriage within 6 weeks?</t>
+  </si>
+  <si>
+    <t>Did she attempt to terminate the pregnancy?</t>
+  </si>
+  <si>
+    <t>Did she die less than 1 year after delivery, abortion or miscarriage?</t>
+  </si>
+  <si>
+    <t>Confirm this was not a maternal death</t>
+  </si>
+  <si>
+    <t>Pregnancy Complications</t>
+  </si>
+  <si>
+    <t>Did she have sharp abdominal pain in the first 3 months of pregnancy?</t>
+  </si>
+  <si>
+    <t>Did she faint when she had the sharp abdominal pain?</t>
+  </si>
+  <si>
+    <t>For how many months was she pregnant?</t>
+  </si>
+  <si>
+    <t>How many babies was she pregnant with?</t>
+  </si>
+  <si>
+    <t>During pregnancy, did she suffer from high blood pressure?</t>
+  </si>
+  <si>
+    <t>Did she have foul smelling vaginal discharge during pregnancy?</t>
+  </si>
+  <si>
+    <t>Did bleeding occur while she was pregnant?</t>
+  </si>
+  <si>
+    <t>Was there vaginal bleeding during the last 3 months of pregnancy?</t>
+  </si>
+  <si>
+    <t>Did she suffer from convulsions during the last 3 months of pregnancy and/or after delivery?</t>
+  </si>
+  <si>
+    <t>Did she have blurred vision during the last 3 months of pregnancy and/or after delivery?</t>
+  </si>
+  <si>
+    <t>Labour &amp; Delivery</t>
+  </si>
+  <si>
+    <t>Did she have excessive bleeding during labour or delivery?</t>
+  </si>
+  <si>
+    <t>Did she have excessive bleeding after delivery?</t>
+  </si>
+  <si>
+    <t>Did she have excessive bleeding during or after abortion or miscarriage?</t>
+  </si>
+  <si>
+    <t>Did she have foul smelling vaginal discharge after delivery/abortion?</t>
+  </si>
+  <si>
+    <t>Did she deliver or try to deliver an abnormally positioned baby?</t>
+  </si>
+  <si>
+    <t>For how many hours was she in labour?</t>
+  </si>
+  <si>
+    <t>Was delivery normal vaginal, without forceps or vacuum?</t>
+  </si>
+  <si>
+    <t>Was delivery vaginal, with forceps or vacuum?</t>
+  </si>
+  <si>
+    <t>Was the delivery a Caesarean section?</t>
+  </si>
+  <si>
+    <t>Was the placenta completely delivered?</t>
+  </si>
+  <si>
+    <t>Where did she give birth?</t>
+  </si>
+  <si>
+    <t>How many births, including stillbirths, did she have before this pregnancy?</t>
+  </si>
+  <si>
+    <t>Had she had any previous Caesarean section?</t>
+  </si>
+  <si>
+    <t>Did she have an operation to remove her uterus shortly before death?</t>
+  </si>
+  <si>
+    <t>ADULT-ONLY VARIABLES (A) - NOT ASKED FOR CHILDREN OR NEONATES</t>
+  </si>
+  <si>
+    <t>Medical History - Adult Only</t>
+  </si>
+  <si>
+    <t>Age Group</t>
+  </si>
+  <si>
+    <t>Adult Only</t>
+  </si>
+  <si>
+    <t>Respiratory &amp; Cardiac - Adult Only</t>
+  </si>
+  <si>
+    <t>Unable to carry out daily routines due to breathlessness</t>
+  </si>
+  <si>
+    <t>Breathless while lying flat</t>
+  </si>
+  <si>
+    <t>Skin Conditions - Adult Only</t>
+  </si>
+  <si>
+    <t>Shingles/herpes zoster</t>
+  </si>
+  <si>
+    <t>Lumps or sores in mouth</t>
+  </si>
+  <si>
+    <t>Lumps anywhere else on body</t>
+  </si>
+  <si>
+    <t>Neurological &amp; Mental - Adult Only</t>
+  </si>
+  <si>
+    <t>Mental confusion</t>
+  </si>
+  <si>
+    <t>COVID-19 - Adult Only</t>
+  </si>
+  <si>
+    <t>Contact with COVID-19 case in two weeks before death</t>
+  </si>
+  <si>
+    <t>Extreme fatigue</t>
+  </si>
+  <si>
+    <t>Loss of smell or taste</t>
+  </si>
+  <si>
+    <t>Risk Factors - Adult Only</t>
+  </si>
+  <si>
+    <t>Alcohol consumption</t>
+  </si>
+  <si>
+    <t>Smoking tobacco</t>
+  </si>
+  <si>
+    <t>Duration of smoking</t>
+  </si>
+  <si>
+    <t>Daily smoking</t>
+  </si>
+  <si>
+    <t>Chewing/sniffing tobacco</t>
+  </si>
+  <si>
+    <t>Duration of chewing/sniffing</t>
+  </si>
+  <si>
+    <t>Daily chewing/sniffing</t>
+  </si>
+  <si>
+    <t>Marital Status - Adult Only</t>
+  </si>
+  <si>
+    <t>Narrative Keywords - Adult Only</t>
+  </si>
+  <si>
+    <t>Key words in narrative (adult-specific)</t>
+  </si>
+  <si>
+    <t>Self-Inflicted Injury - Age 10+ Only</t>
+  </si>
+  <si>
+    <t>Was injury self-inflicted?</t>
+  </si>
+  <si>
+    <t>Age 10+ Only</t>
+  </si>
+  <si>
+    <t>VARIABLES ASKED FOR CHILDREN ONLY (C) - NOT ADULTS OR NEONATES</t>
+  </si>
+  <si>
+    <t>Id10169</t>
+  </si>
+  <si>
+    <t>Not present</t>
+  </si>
+  <si>
+    <t>Child Only</t>
+  </si>
+  <si>
+    <t>Sunken eyes</t>
+  </si>
+  <si>
+    <t>Complications during labour/delivery</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -13121,6 +14307,32 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -13177,7 +14389,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -13358,6 +14570,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -44766,7 +45985,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="292" spans="1:18" s="26" customFormat="1" ht="45">
+    <row r="292" spans="1:18" s="26" customFormat="1" ht="30">
       <c r="A292" s="26" t="s">
         <v>25</v>
       </c>
@@ -48781,7 +50000,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="435" spans="1:17" s="26" customFormat="1" ht="45">
+    <row r="435" spans="1:17" s="26" customFormat="1" ht="30">
       <c r="A435" s="26" t="s">
         <v>79</v>
       </c>
@@ -51256,7 +52475,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="539" spans="1:11" s="26" customFormat="1" ht="45">
+    <row r="539" spans="1:11" s="26" customFormat="1" ht="30">
       <c r="A539" s="26" t="s">
         <v>79</v>
       </c>
@@ -53360,7 +54579,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="32">
+    <row r="29" spans="1:4" ht="48">
       <c r="A29" t="s">
         <v>1738</v>
       </c>
@@ -72602,6 +73821,6449 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A42C50-7BFF-914F-92FF-FBBA488F3E3C}">
+  <dimension ref="A1:E444"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="94" t="s">
+        <v>4178</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C2" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E2" s="95"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="97" t="s">
+        <v>4183</v>
+      </c>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="95" t="s">
+        <v>3630</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>3631</v>
+      </c>
+      <c r="C4" s="95" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>4184</v>
+      </c>
+      <c r="E4" s="95"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="95" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>3635</v>
+      </c>
+      <c r="C5" s="95" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D5" s="95" t="s">
+        <v>4185</v>
+      </c>
+      <c r="E5" s="95"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>3639</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="95" t="s">
+        <v>4186</v>
+      </c>
+      <c r="E6" s="95"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="95" t="s">
+        <v>3642</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>3643</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>3642</v>
+      </c>
+      <c r="D7" s="95" t="s">
+        <v>3643</v>
+      </c>
+      <c r="E7" s="95"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="95" t="s">
+        <v>3645</v>
+      </c>
+      <c r="B8" s="95" t="s">
+        <v>3646</v>
+      </c>
+      <c r="C8" s="95" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D8" s="95" t="s">
+        <v>3646</v>
+      </c>
+      <c r="E8" s="95"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>4187</v>
+      </c>
+      <c r="C9" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="95" t="s">
+        <v>4187</v>
+      </c>
+      <c r="E9" s="95"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="97" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B10" s="97"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C11" s="95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="95" t="s">
+        <v>4189</v>
+      </c>
+      <c r="E11" s="95"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>4190</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="95" t="s">
+        <v>4190</v>
+      </c>
+      <c r="E12" s="95"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>4191</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="95" t="s">
+        <v>4191</v>
+      </c>
+      <c r="E13" s="95"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="95" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>4192</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="95" t="s">
+        <v>4192</v>
+      </c>
+      <c r="E14" s="95"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="95"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="97" t="s">
+        <v>4193</v>
+      </c>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="95" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="95" t="s">
+        <v>4194</v>
+      </c>
+      <c r="C17" s="95" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="95" t="s">
+        <v>4194</v>
+      </c>
+      <c r="E17" s="95"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="95" t="s">
+        <v>4195</v>
+      </c>
+      <c r="C18" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="95" t="s">
+        <v>4195</v>
+      </c>
+      <c r="E18" s="95"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="95" t="s">
+        <v>4196</v>
+      </c>
+      <c r="C19" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="95" t="s">
+        <v>4196</v>
+      </c>
+      <c r="E19" s="95"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="97" t="s">
+        <v>4197</v>
+      </c>
+      <c r="B20" s="97"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="95" t="s">
+        <v>4198</v>
+      </c>
+      <c r="C21" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="95" t="s">
+        <v>4198</v>
+      </c>
+      <c r="E21" s="95"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="95" t="s">
+        <v>4199</v>
+      </c>
+      <c r="E22" s="95"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>4200</v>
+      </c>
+      <c r="C23" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="95" t="s">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="95"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="95" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>4201</v>
+      </c>
+      <c r="C24" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D24" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E24" s="95"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="95" t="s">
+        <v>4204</v>
+      </c>
+      <c r="C25" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="95" t="s">
+        <v>4204</v>
+      </c>
+      <c r="E25" s="95"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="95" t="s">
+        <v>4205</v>
+      </c>
+      <c r="C26" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="95" t="s">
+        <v>4205</v>
+      </c>
+      <c r="E26" s="95"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="95" t="s">
+        <v>4206</v>
+      </c>
+      <c r="C27" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="95" t="s">
+        <v>4206</v>
+      </c>
+      <c r="E27" s="95"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="95" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B28" s="95" t="s">
+        <v>4207</v>
+      </c>
+      <c r="C28" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D28" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E28" s="95"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="95" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B29" s="95" t="s">
+        <v>4208</v>
+      </c>
+      <c r="C29" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D29" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E29" s="95"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="95" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>4209</v>
+      </c>
+      <c r="C30" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D30" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E30" s="95"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="95" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B31" s="95" t="s">
+        <v>4210</v>
+      </c>
+      <c r="C31" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D31" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E31" s="95"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="95" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B32" s="95" t="s">
+        <v>4211</v>
+      </c>
+      <c r="C32" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E32" s="95"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="95" t="s">
+        <v>3692</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>4212</v>
+      </c>
+      <c r="C33" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D33" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E33" s="95"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" s="95" t="s">
+        <v>4213</v>
+      </c>
+      <c r="C34" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="95" t="s">
+        <v>4213</v>
+      </c>
+      <c r="E34" s="95"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="95" t="s">
+        <v>4184</v>
+      </c>
+      <c r="C35" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="95" t="s">
+        <v>4184</v>
+      </c>
+      <c r="E35" s="95"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="95"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="94" t="s">
+        <v>4214</v>
+      </c>
+      <c r="B37" s="94"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B38" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C38" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D38" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E38" s="95"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="95" t="s">
+        <v>4215</v>
+      </c>
+      <c r="C39" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="95" t="s">
+        <v>4215</v>
+      </c>
+      <c r="E39" s="95"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="95" t="s">
+        <v>4216</v>
+      </c>
+      <c r="C40" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="95" t="s">
+        <v>4216</v>
+      </c>
+      <c r="E40" s="95"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="95" t="s">
+        <v>4217</v>
+      </c>
+      <c r="C41" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="95" t="s">
+        <v>4217</v>
+      </c>
+      <c r="E41" s="95"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="95" t="s">
+        <v>4218</v>
+      </c>
+      <c r="C42" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="95" t="s">
+        <v>4218</v>
+      </c>
+      <c r="E42" s="95"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="95" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="95" t="s">
+        <v>4219</v>
+      </c>
+      <c r="C43" s="95" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="95" t="s">
+        <v>4219</v>
+      </c>
+      <c r="E43" s="95"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="95" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="95" t="s">
+        <v>4220</v>
+      </c>
+      <c r="C44" s="95" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="95" t="s">
+        <v>4220</v>
+      </c>
+      <c r="E44" s="95"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="95" t="s">
+        <v>4221</v>
+      </c>
+      <c r="C45" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="95" t="s">
+        <v>4221</v>
+      </c>
+      <c r="E45" s="95"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="95" t="s">
+        <v>4222</v>
+      </c>
+      <c r="C46" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="95" t="s">
+        <v>4222</v>
+      </c>
+      <c r="E46" s="95"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" s="95" t="s">
+        <v>4223</v>
+      </c>
+      <c r="C47" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="95" t="s">
+        <v>4223</v>
+      </c>
+      <c r="E47" s="95"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="95" t="s">
+        <v>133</v>
+      </c>
+      <c r="B48" s="95" t="s">
+        <v>4224</v>
+      </c>
+      <c r="C48" s="95" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" s="95" t="s">
+        <v>4224</v>
+      </c>
+      <c r="E48" s="95"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="C49" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="E49" s="95"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="95" t="s">
+        <v>4225</v>
+      </c>
+      <c r="C50" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="95" t="s">
+        <v>4225</v>
+      </c>
+      <c r="E50" s="95"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="95" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="95" t="s">
+        <v>4226</v>
+      </c>
+      <c r="C51" s="95" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="95" t="s">
+        <v>4226</v>
+      </c>
+      <c r="E51" s="95"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="95" t="s">
+        <v>262</v>
+      </c>
+      <c r="B52" s="95" t="s">
+        <v>4227</v>
+      </c>
+      <c r="C52" s="95" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="95" t="s">
+        <v>4227</v>
+      </c>
+      <c r="E52" s="95"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="95" t="s">
+        <v>264</v>
+      </c>
+      <c r="B53" s="95" t="s">
+        <v>4228</v>
+      </c>
+      <c r="C53" s="95" t="s">
+        <v>264</v>
+      </c>
+      <c r="D53" s="95" t="s">
+        <v>4228</v>
+      </c>
+      <c r="E53" s="95"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="B54" s="95" t="s">
+        <v>4229</v>
+      </c>
+      <c r="C54" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="D54" s="95" t="s">
+        <v>4229</v>
+      </c>
+      <c r="E54" s="95"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="95" t="s">
+        <v>4230</v>
+      </c>
+      <c r="C55" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" s="95" t="s">
+        <v>4230</v>
+      </c>
+      <c r="E55" s="95"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" s="95" t="s">
+        <v>4231</v>
+      </c>
+      <c r="C56" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" s="95" t="s">
+        <v>4231</v>
+      </c>
+      <c r="E56" s="95"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="95" t="s">
+        <v>4232</v>
+      </c>
+      <c r="C57" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" s="95" t="s">
+        <v>4232</v>
+      </c>
+      <c r="E57" s="95"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="95" t="s">
+        <v>217</v>
+      </c>
+      <c r="B58" s="95" t="s">
+        <v>4233</v>
+      </c>
+      <c r="C58" s="95" t="s">
+        <v>217</v>
+      </c>
+      <c r="D58" s="95" t="s">
+        <v>4233</v>
+      </c>
+      <c r="E58" s="95"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="95" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="95" t="s">
+        <v>4234</v>
+      </c>
+      <c r="C59" s="95" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59" s="95" t="s">
+        <v>4234</v>
+      </c>
+      <c r="E59" s="95"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="95" t="s">
+        <v>228</v>
+      </c>
+      <c r="B60" s="95" t="s">
+        <v>4235</v>
+      </c>
+      <c r="C60" s="95" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="95" t="s">
+        <v>4235</v>
+      </c>
+      <c r="E60" s="95"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="95" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="95" t="s">
+        <v>4236</v>
+      </c>
+      <c r="C61" s="95" t="s">
+        <v>234</v>
+      </c>
+      <c r="D61" s="95" t="s">
+        <v>4236</v>
+      </c>
+      <c r="E61" s="95"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="95" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" s="95" t="s">
+        <v>4237</v>
+      </c>
+      <c r="C62" s="95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="95" t="s">
+        <v>4237</v>
+      </c>
+      <c r="E62" s="95"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="95" t="s">
+        <v>276</v>
+      </c>
+      <c r="B63" s="95" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C63" s="95" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" s="95" t="s">
+        <v>4238</v>
+      </c>
+      <c r="E63" s="95"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="95" t="s">
+        <v>4111</v>
+      </c>
+      <c r="B64" s="95" t="s">
+        <v>4239</v>
+      </c>
+      <c r="C64" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D64" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E64" s="95"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="95"/>
+      <c r="B65" s="95"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="95"/>
+      <c r="E65" s="95"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="94" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B66" s="94"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="95"/>
+      <c r="E66" s="95"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B67" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C67" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D67" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E67" s="95"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="95" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" s="95" t="s">
+        <v>4241</v>
+      </c>
+      <c r="C68" s="95" t="s">
+        <v>282</v>
+      </c>
+      <c r="D68" s="95" t="s">
+        <v>4241</v>
+      </c>
+      <c r="E68" s="95"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="95" t="s">
+        <v>287</v>
+      </c>
+      <c r="B69" s="95" t="s">
+        <v>4242</v>
+      </c>
+      <c r="C69" s="95" t="s">
+        <v>287</v>
+      </c>
+      <c r="D69" s="95" t="s">
+        <v>4242</v>
+      </c>
+      <c r="E69" s="95"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="95" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" s="95" t="s">
+        <v>4243</v>
+      </c>
+      <c r="C70" s="95" t="s">
+        <v>290</v>
+      </c>
+      <c r="D70" s="95" t="s">
+        <v>4243</v>
+      </c>
+      <c r="E70" s="95"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="95" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B71" s="95" t="s">
+        <v>4245</v>
+      </c>
+      <c r="C71" s="95" t="s">
+        <v>4244</v>
+      </c>
+      <c r="D71" s="95" t="s">
+        <v>4245</v>
+      </c>
+      <c r="E71" s="95"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="95" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B72" s="95" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C72" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D72" s="98" t="s">
+        <v>4246</v>
+      </c>
+      <c r="E72" s="95"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="95" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B73" s="95" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C73" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D73" s="98" t="s">
+        <v>4246</v>
+      </c>
+      <c r="E73" s="95"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="95" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B74" s="95" t="s">
+        <v>4247</v>
+      </c>
+      <c r="C74" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D74" s="98" t="s">
+        <v>4246</v>
+      </c>
+      <c r="E74" s="95"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="95" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B75" s="95" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C75" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D75" s="98" t="s">
+        <v>4246</v>
+      </c>
+      <c r="E75" s="95"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" s="95" t="s">
+        <v>4248</v>
+      </c>
+      <c r="C76" s="95" t="s">
+        <v>295</v>
+      </c>
+      <c r="D76" s="95" t="s">
+        <v>4248</v>
+      </c>
+      <c r="E76" s="95"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="95" t="s">
+        <v>299</v>
+      </c>
+      <c r="B77" s="95" t="s">
+        <v>4249</v>
+      </c>
+      <c r="C77" s="95" t="s">
+        <v>299</v>
+      </c>
+      <c r="D77" s="95" t="s">
+        <v>4249</v>
+      </c>
+      <c r="E77" s="95"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="95" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B78" s="95" t="s">
+        <v>4250</v>
+      </c>
+      <c r="C78" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D78" s="98" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E78" s="95"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="95" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B79" s="95" t="s">
+        <v>4252</v>
+      </c>
+      <c r="C79" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D79" s="98" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E79" s="95"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="95" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B80" s="95" t="s">
+        <v>4253</v>
+      </c>
+      <c r="C80" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D80" s="98" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E80" s="95"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="95" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B81" s="95" t="s">
+        <v>4254</v>
+      </c>
+      <c r="C81" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D81" s="98" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E81" s="95"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="95" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B82" s="95" t="s">
+        <v>4255</v>
+      </c>
+      <c r="C82" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D82" s="98" t="s">
+        <v>4251</v>
+      </c>
+      <c r="E82" s="95"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="B83" s="95" t="s">
+        <v>4256</v>
+      </c>
+      <c r="C83" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="D83" s="95" t="s">
+        <v>4256</v>
+      </c>
+      <c r="E83" s="95"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="95" t="s">
+        <v>308</v>
+      </c>
+      <c r="B84" s="95" t="s">
+        <v>4257</v>
+      </c>
+      <c r="C84" s="95" t="s">
+        <v>308</v>
+      </c>
+      <c r="D84" s="95" t="s">
+        <v>4257</v>
+      </c>
+      <c r="E84" s="95"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="95" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" s="95" t="s">
+        <v>4258</v>
+      </c>
+      <c r="C85" s="95" t="s">
+        <v>312</v>
+      </c>
+      <c r="D85" s="95" t="s">
+        <v>4258</v>
+      </c>
+      <c r="E85" s="95"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="95" t="s">
+        <v>318</v>
+      </c>
+      <c r="B86" s="95" t="s">
+        <v>4259</v>
+      </c>
+      <c r="C86" s="95" t="s">
+        <v>318</v>
+      </c>
+      <c r="D86" s="95" t="s">
+        <v>4259</v>
+      </c>
+      <c r="E86" s="95"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="95" t="s">
+        <v>323</v>
+      </c>
+      <c r="B87" s="95" t="s">
+        <v>4260</v>
+      </c>
+      <c r="C87" s="95" t="s">
+        <v>323</v>
+      </c>
+      <c r="D87" s="95" t="s">
+        <v>4260</v>
+      </c>
+      <c r="E87" s="95"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="95" t="s">
+        <v>326</v>
+      </c>
+      <c r="B88" s="95" t="s">
+        <v>4261</v>
+      </c>
+      <c r="C88" s="95" t="s">
+        <v>326</v>
+      </c>
+      <c r="D88" s="95" t="s">
+        <v>4261</v>
+      </c>
+      <c r="E88" s="95"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="B89" s="95" t="s">
+        <v>4262</v>
+      </c>
+      <c r="C89" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="D89" s="95" t="s">
+        <v>4262</v>
+      </c>
+      <c r="E89" s="95"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="95"/>
+      <c r="B90" s="95"/>
+      <c r="C90" s="95"/>
+      <c r="D90" s="95"/>
+      <c r="E90" s="95"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="94" t="s">
+        <v>4263</v>
+      </c>
+      <c r="B91" s="94"/>
+      <c r="C91" s="95"/>
+      <c r="D91" s="95"/>
+      <c r="E91" s="95"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B92" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C92" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D92" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E92" s="95"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="B93" s="95" t="s">
+        <v>4264</v>
+      </c>
+      <c r="C93" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D93" s="95" t="s">
+        <v>4264</v>
+      </c>
+      <c r="E93" s="95"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="95" t="s">
+        <v>343</v>
+      </c>
+      <c r="B94" s="95" t="s">
+        <v>4265</v>
+      </c>
+      <c r="C94" s="95" t="s">
+        <v>343</v>
+      </c>
+      <c r="D94" s="95" t="s">
+        <v>4265</v>
+      </c>
+      <c r="E94" s="95"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="B95" s="95" t="s">
+        <v>4266</v>
+      </c>
+      <c r="C95" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="D95" s="95" t="s">
+        <v>4266</v>
+      </c>
+      <c r="E95" s="95"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="95" t="s">
+        <v>355</v>
+      </c>
+      <c r="B96" s="95" t="s">
+        <v>4267</v>
+      </c>
+      <c r="C96" s="95" t="s">
+        <v>355</v>
+      </c>
+      <c r="D96" s="95" t="s">
+        <v>4267</v>
+      </c>
+      <c r="E96" s="95"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="95" t="s">
+        <v>359</v>
+      </c>
+      <c r="B97" s="95" t="s">
+        <v>4268</v>
+      </c>
+      <c r="C97" s="95" t="s">
+        <v>359</v>
+      </c>
+      <c r="D97" s="95" t="s">
+        <v>4268</v>
+      </c>
+      <c r="E97" s="95"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="95" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B98" s="95" t="s">
+        <v>4269</v>
+      </c>
+      <c r="C98" s="95" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D98" s="95" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E98" s="95"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="95" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B99" s="95" t="s">
+        <v>4270</v>
+      </c>
+      <c r="C99" s="95" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D99" s="95" t="s">
+        <v>4270</v>
+      </c>
+      <c r="E99" s="95"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="95" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B100" s="95" t="s">
+        <v>4271</v>
+      </c>
+      <c r="C100" s="95" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D100" s="95" t="s">
+        <v>4271</v>
+      </c>
+      <c r="E100" s="95"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="95" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B101" s="95" t="s">
+        <v>4272</v>
+      </c>
+      <c r="C101" s="95" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D101" s="95" t="s">
+        <v>4272</v>
+      </c>
+      <c r="E101" s="95"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="95" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B102" s="95" t="s">
+        <v>4273</v>
+      </c>
+      <c r="C102" s="95" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D102" s="95" t="s">
+        <v>4273</v>
+      </c>
+      <c r="E102" s="95"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="95" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B103" s="95" t="s">
+        <v>4274</v>
+      </c>
+      <c r="C103" s="95" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D103" s="95" t="s">
+        <v>4274</v>
+      </c>
+      <c r="E103" s="95"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="95" t="s">
+        <v>3588</v>
+      </c>
+      <c r="B104" s="95" t="s">
+        <v>4275</v>
+      </c>
+      <c r="C104" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D104" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E104" s="95"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="95" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B105" s="95" t="s">
+        <v>4276</v>
+      </c>
+      <c r="C105" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D105" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E105" s="95"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="95" t="s">
+        <v>3599</v>
+      </c>
+      <c r="B106" s="95" t="s">
+        <v>4277</v>
+      </c>
+      <c r="C106" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D106" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E106" s="95"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="95" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B107" s="95" t="s">
+        <v>4278</v>
+      </c>
+      <c r="C107" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D107" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E107" s="95"/>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="95" t="s">
+        <v>3610</v>
+      </c>
+      <c r="B108" s="95" t="s">
+        <v>4279</v>
+      </c>
+      <c r="C108" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D108" s="98" t="s">
+        <v>4203</v>
+      </c>
+      <c r="E108" s="95"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="95"/>
+      <c r="B109" s="95"/>
+      <c r="C109" s="95"/>
+      <c r="D109" s="95"/>
+      <c r="E109" s="95"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="94" t="s">
+        <v>4280</v>
+      </c>
+      <c r="B110" s="94"/>
+      <c r="C110" s="95"/>
+      <c r="D110" s="95"/>
+      <c r="E110" s="95"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B111" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C111" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D111" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E111" s="95"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="95" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B112" s="95" t="s">
+        <v>4281</v>
+      </c>
+      <c r="C112" s="95" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D112" s="95" t="s">
+        <v>4281</v>
+      </c>
+      <c r="E112" s="95"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="95" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B113" s="95" t="s">
+        <v>4282</v>
+      </c>
+      <c r="C113" s="95" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D113" s="95" t="s">
+        <v>4282</v>
+      </c>
+      <c r="E113" s="95"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="95" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B114" s="95" t="s">
+        <v>4283</v>
+      </c>
+      <c r="C114" s="95" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D114" s="95" t="s">
+        <v>4283</v>
+      </c>
+      <c r="E114" s="95"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="95" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B115" s="95" t="s">
+        <v>4284</v>
+      </c>
+      <c r="C115" s="95" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D115" s="95" t="s">
+        <v>4284</v>
+      </c>
+      <c r="E115" s="95"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="95" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B116" s="95" t="s">
+        <v>4285</v>
+      </c>
+      <c r="C116" s="95" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D116" s="95" t="s">
+        <v>4285</v>
+      </c>
+      <c r="E116" s="95"/>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="95" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B117" s="95" t="s">
+        <v>4286</v>
+      </c>
+      <c r="C117" s="95" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D117" s="95" t="s">
+        <v>4286</v>
+      </c>
+      <c r="E117" s="95"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="95" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B118" s="95" t="s">
+        <v>4287</v>
+      </c>
+      <c r="C118" s="95" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D118" s="95" t="s">
+        <v>4287</v>
+      </c>
+      <c r="E118" s="95"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="95" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B119" s="95" t="s">
+        <v>4288</v>
+      </c>
+      <c r="C119" s="95" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D119" s="95" t="s">
+        <v>4288</v>
+      </c>
+      <c r="E119" s="95"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="95" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B120" s="95" t="s">
+        <v>4289</v>
+      </c>
+      <c r="C120" s="95" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D120" s="95" t="s">
+        <v>4289</v>
+      </c>
+      <c r="E120" s="95"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="95" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B121" s="95" t="s">
+        <v>4290</v>
+      </c>
+      <c r="C121" s="95" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D121" s="95" t="s">
+        <v>4290</v>
+      </c>
+      <c r="E121" s="95"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="95" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B122" s="95" t="s">
+        <v>4291</v>
+      </c>
+      <c r="C122" s="95" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D122" s="95" t="s">
+        <v>4291</v>
+      </c>
+      <c r="E122" s="95"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="95" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B123" s="95" t="s">
+        <v>4292</v>
+      </c>
+      <c r="C123" s="95" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D123" s="95" t="s">
+        <v>4292</v>
+      </c>
+      <c r="E123" s="95"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="95"/>
+      <c r="B124" s="95"/>
+      <c r="C124" s="95"/>
+      <c r="D124" s="95"/>
+      <c r="E124" s="95"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="94" t="s">
+        <v>4293</v>
+      </c>
+      <c r="B125" s="94"/>
+      <c r="C125" s="94"/>
+      <c r="D125" s="95"/>
+      <c r="E125" s="95"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B126" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C126" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D126" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E126" s="95"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="B127" s="95" t="s">
+        <v>4294</v>
+      </c>
+      <c r="C127" s="95" t="s">
+        <v>369</v>
+      </c>
+      <c r="D127" s="95" t="s">
+        <v>4294</v>
+      </c>
+      <c r="E127" s="95"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="95" t="s">
+        <v>371</v>
+      </c>
+      <c r="B128" s="95" t="s">
+        <v>4295</v>
+      </c>
+      <c r="C128" s="95" t="s">
+        <v>371</v>
+      </c>
+      <c r="D128" s="95" t="s">
+        <v>4295</v>
+      </c>
+      <c r="E128" s="95"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="95" t="s">
+        <v>374</v>
+      </c>
+      <c r="B129" s="95" t="s">
+        <v>4296</v>
+      </c>
+      <c r="C129" s="95" t="s">
+        <v>374</v>
+      </c>
+      <c r="D129" s="95" t="s">
+        <v>4296</v>
+      </c>
+      <c r="E129" s="95"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="95" t="s">
+        <v>381</v>
+      </c>
+      <c r="B130" s="95" t="s">
+        <v>4297</v>
+      </c>
+      <c r="C130" s="95" t="s">
+        <v>381</v>
+      </c>
+      <c r="D130" s="95" t="s">
+        <v>4297</v>
+      </c>
+      <c r="E130" s="95"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="B131" s="95" t="s">
+        <v>4298</v>
+      </c>
+      <c r="C131" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="D131" s="95" t="s">
+        <v>4298</v>
+      </c>
+      <c r="E131" s="95"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="95" t="s">
+        <v>387</v>
+      </c>
+      <c r="B132" s="95" t="s">
+        <v>4299</v>
+      </c>
+      <c r="C132" s="95" t="s">
+        <v>387</v>
+      </c>
+      <c r="D132" s="95" t="s">
+        <v>4299</v>
+      </c>
+      <c r="E132" s="95"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="95" t="s">
+        <v>390</v>
+      </c>
+      <c r="B133" s="95" t="s">
+        <v>4300</v>
+      </c>
+      <c r="C133" s="95" t="s">
+        <v>390</v>
+      </c>
+      <c r="D133" s="95" t="s">
+        <v>4300</v>
+      </c>
+      <c r="E133" s="95"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="95" t="s">
+        <v>392</v>
+      </c>
+      <c r="B134" s="95" t="s">
+        <v>4301</v>
+      </c>
+      <c r="C134" s="95" t="s">
+        <v>392</v>
+      </c>
+      <c r="D134" s="95" t="s">
+        <v>4301</v>
+      </c>
+      <c r="E134" s="95"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="95" t="s">
+        <v>394</v>
+      </c>
+      <c r="B135" s="95" t="s">
+        <v>4302</v>
+      </c>
+      <c r="C135" s="95" t="s">
+        <v>394</v>
+      </c>
+      <c r="D135" s="95" t="s">
+        <v>4302</v>
+      </c>
+      <c r="E135" s="95"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="95" t="s">
+        <v>397</v>
+      </c>
+      <c r="B136" s="95" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C136" s="95" t="s">
+        <v>397</v>
+      </c>
+      <c r="D136" s="95" t="s">
+        <v>4303</v>
+      </c>
+      <c r="E136" s="95"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="95" t="s">
+        <v>400</v>
+      </c>
+      <c r="B137" s="95" t="s">
+        <v>4304</v>
+      </c>
+      <c r="C137" s="95" t="s">
+        <v>400</v>
+      </c>
+      <c r="D137" s="95" t="s">
+        <v>4304</v>
+      </c>
+      <c r="E137" s="95"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="95" t="s">
+        <v>402</v>
+      </c>
+      <c r="B138" s="95" t="s">
+        <v>4305</v>
+      </c>
+      <c r="C138" s="95" t="s">
+        <v>402</v>
+      </c>
+      <c r="D138" s="95" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E138" s="95"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="B139" s="95" t="s">
+        <v>4306</v>
+      </c>
+      <c r="C139" s="95" t="s">
+        <v>407</v>
+      </c>
+      <c r="D139" s="95" t="s">
+        <v>4306</v>
+      </c>
+      <c r="E139" s="95"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="95" t="s">
+        <v>409</v>
+      </c>
+      <c r="B140" s="95" t="s">
+        <v>4307</v>
+      </c>
+      <c r="C140" s="95" t="s">
+        <v>409</v>
+      </c>
+      <c r="D140" s="95" t="s">
+        <v>4307</v>
+      </c>
+      <c r="E140" s="95"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="95" t="s">
+        <v>565</v>
+      </c>
+      <c r="B141" s="95" t="s">
+        <v>4308</v>
+      </c>
+      <c r="C141" s="95" t="s">
+        <v>565</v>
+      </c>
+      <c r="D141" s="95" t="s">
+        <v>4308</v>
+      </c>
+      <c r="E141" s="95"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="95" t="s">
+        <v>573</v>
+      </c>
+      <c r="B142" s="95" t="s">
+        <v>4309</v>
+      </c>
+      <c r="C142" s="95" t="s">
+        <v>573</v>
+      </c>
+      <c r="D142" s="95" t="s">
+        <v>4309</v>
+      </c>
+      <c r="E142" s="95"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="95" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B143" s="95" t="s">
+        <v>4310</v>
+      </c>
+      <c r="C143" s="95" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D143" s="95" t="s">
+        <v>4310</v>
+      </c>
+      <c r="E143" s="95"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="95" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B144" s="95" t="s">
+        <v>4311</v>
+      </c>
+      <c r="C144" s="95" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D144" s="95" t="s">
+        <v>4311</v>
+      </c>
+      <c r="E144" s="95"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="95" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B145" s="95" t="s">
+        <v>4312</v>
+      </c>
+      <c r="C145" s="95" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D145" s="95" t="s">
+        <v>4312</v>
+      </c>
+      <c r="E145" s="95"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="95" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B146" s="95" t="s">
+        <v>4313</v>
+      </c>
+      <c r="C146" s="95" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D146" s="95" t="s">
+        <v>4313</v>
+      </c>
+      <c r="E146" s="95"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="95" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B147" s="95" t="s">
+        <v>4314</v>
+      </c>
+      <c r="C147" s="95" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D147" s="95" t="s">
+        <v>4314</v>
+      </c>
+      <c r="E147" s="95"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="95" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B148" s="95" t="s">
+        <v>4315</v>
+      </c>
+      <c r="C148" s="95" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D148" s="95" t="s">
+        <v>4315</v>
+      </c>
+      <c r="E148" s="95"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="95" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B149" s="95" t="s">
+        <v>4316</v>
+      </c>
+      <c r="C149" s="95" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D149" s="95" t="s">
+        <v>4316</v>
+      </c>
+      <c r="E149" s="95"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="95" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B150" s="95" t="s">
+        <v>4317</v>
+      </c>
+      <c r="C150" s="95" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D150" s="95" t="s">
+        <v>4317</v>
+      </c>
+      <c r="E150" s="95"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="95" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B151" s="95" t="s">
+        <v>4318</v>
+      </c>
+      <c r="C151" s="95" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D151" s="95" t="s">
+        <v>4318</v>
+      </c>
+      <c r="E151" s="95"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="95" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B152" s="95" t="s">
+        <v>4319</v>
+      </c>
+      <c r="C152" s="95" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D152" s="95" t="s">
+        <v>4319</v>
+      </c>
+      <c r="E152" s="95"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="95" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B153" s="95" t="s">
+        <v>4320</v>
+      </c>
+      <c r="C153" s="95" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D153" s="95" t="s">
+        <v>4320</v>
+      </c>
+      <c r="E153" s="95"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="95" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B154" s="95" t="s">
+        <v>4321</v>
+      </c>
+      <c r="C154" s="95" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D154" s="95" t="s">
+        <v>4321</v>
+      </c>
+      <c r="E154" s="95"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="95" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B155" s="95" t="s">
+        <v>4322</v>
+      </c>
+      <c r="C155" s="95" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D155" s="95" t="s">
+        <v>4322</v>
+      </c>
+      <c r="E155" s="95"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="95" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B156" s="95" t="s">
+        <v>4323</v>
+      </c>
+      <c r="C156" s="95" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D156" s="95" t="s">
+        <v>4323</v>
+      </c>
+      <c r="E156" s="95"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="95" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B157" s="95" t="s">
+        <v>4324</v>
+      </c>
+      <c r="C157" s="95" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D157" s="95" t="s">
+        <v>4324</v>
+      </c>
+      <c r="E157" s="95"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="95" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B158" s="95" t="s">
+        <v>4325</v>
+      </c>
+      <c r="C158" s="95" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D158" s="95" t="s">
+        <v>4325</v>
+      </c>
+      <c r="E158" s="95"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="95" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B159" s="95" t="s">
+        <v>4326</v>
+      </c>
+      <c r="C159" s="95" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D159" s="95" t="s">
+        <v>4326</v>
+      </c>
+      <c r="E159" s="95"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="95" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B160" s="95" t="s">
+        <v>4327</v>
+      </c>
+      <c r="C160" s="95" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D160" s="95" t="s">
+        <v>4327</v>
+      </c>
+      <c r="E160" s="95"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="95" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B161" s="95" t="s">
+        <v>4328</v>
+      </c>
+      <c r="C161" s="95" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D161" s="95" t="s">
+        <v>4328</v>
+      </c>
+      <c r="E161" s="95"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="95" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B162" s="95" t="s">
+        <v>4329</v>
+      </c>
+      <c r="C162" s="95" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D162" s="95" t="s">
+        <v>4329</v>
+      </c>
+      <c r="E162" s="95"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="95" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B163" s="95" t="s">
+        <v>4330</v>
+      </c>
+      <c r="C163" s="95" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D163" s="95" t="s">
+        <v>4330</v>
+      </c>
+      <c r="E163" s="95"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="95" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B164" s="95" t="s">
+        <v>4331</v>
+      </c>
+      <c r="C164" s="95" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D164" s="95" t="s">
+        <v>4331</v>
+      </c>
+      <c r="E164" s="95"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="95" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B165" s="95" t="s">
+        <v>4332</v>
+      </c>
+      <c r="C165" s="95" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D165" s="95" t="s">
+        <v>4332</v>
+      </c>
+      <c r="E165" s="95"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="95" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B166" s="95" t="s">
+        <v>4333</v>
+      </c>
+      <c r="C166" s="95" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D166" s="95" t="s">
+        <v>4333</v>
+      </c>
+      <c r="E166" s="95"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="95" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B167" s="95" t="s">
+        <v>4334</v>
+      </c>
+      <c r="C167" s="95" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D167" s="95" t="s">
+        <v>4334</v>
+      </c>
+      <c r="E167" s="95"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="95" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B168" s="95" t="s">
+        <v>4335</v>
+      </c>
+      <c r="C168" s="95" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D168" s="95" t="s">
+        <v>4335</v>
+      </c>
+      <c r="E168" s="95"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="95" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B169" s="95" t="s">
+        <v>4336</v>
+      </c>
+      <c r="C169" s="95" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D169" s="95" t="s">
+        <v>4336</v>
+      </c>
+      <c r="E169" s="95"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="95" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B170" s="95" t="s">
+        <v>4337</v>
+      </c>
+      <c r="C170" s="95" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D170" s="95" t="s">
+        <v>4337</v>
+      </c>
+      <c r="E170" s="95"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="95" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B171" s="95" t="s">
+        <v>4338</v>
+      </c>
+      <c r="C171" s="95" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D171" s="95" t="s">
+        <v>4338</v>
+      </c>
+      <c r="E171" s="95"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="95" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B172" s="95" t="s">
+        <v>4339</v>
+      </c>
+      <c r="C172" s="95" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D172" s="95" t="s">
+        <v>4339</v>
+      </c>
+      <c r="E172" s="95"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="95" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B173" s="95" t="s">
+        <v>4340</v>
+      </c>
+      <c r="C173" s="95" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D173" s="95" t="s">
+        <v>4340</v>
+      </c>
+      <c r="E173" s="95"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="95" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B174" s="95" t="s">
+        <v>4341</v>
+      </c>
+      <c r="C174" s="95" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D174" s="95" t="s">
+        <v>4341</v>
+      </c>
+      <c r="E174" s="95"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="95" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B175" s="95" t="s">
+        <v>4342</v>
+      </c>
+      <c r="C175" s="95" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D175" s="95" t="s">
+        <v>4342</v>
+      </c>
+      <c r="E175" s="95"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="95" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B176" s="95" t="s">
+        <v>4343</v>
+      </c>
+      <c r="C176" s="95" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D176" s="95" t="s">
+        <v>4343</v>
+      </c>
+      <c r="E176" s="95"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="95" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B177" s="95" t="s">
+        <v>4344</v>
+      </c>
+      <c r="C177" s="95" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D177" s="95" t="s">
+        <v>4344</v>
+      </c>
+      <c r="E177" s="95"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="95" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B178" s="95" t="s">
+        <v>4345</v>
+      </c>
+      <c r="C178" s="95" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D178" s="95" t="s">
+        <v>4345</v>
+      </c>
+      <c r="E178" s="95"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="95" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B179" s="95" t="s">
+        <v>4346</v>
+      </c>
+      <c r="C179" s="95" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D179" s="95" t="s">
+        <v>4346</v>
+      </c>
+      <c r="E179" s="95"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="95" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B180" s="95" t="s">
+        <v>4347</v>
+      </c>
+      <c r="C180" s="95" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D180" s="95" t="s">
+        <v>4347</v>
+      </c>
+      <c r="E180" s="95"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="95" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B181" s="95" t="s">
+        <v>4348</v>
+      </c>
+      <c r="C181" s="95" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D181" s="95" t="s">
+        <v>4348</v>
+      </c>
+      <c r="E181" s="95"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="95" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B182" s="95" t="s">
+        <v>4349</v>
+      </c>
+      <c r="C182" s="95" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D182" s="95" t="s">
+        <v>4349</v>
+      </c>
+      <c r="E182" s="95"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="95" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B183" s="95" t="s">
+        <v>4350</v>
+      </c>
+      <c r="C183" s="95" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D183" s="95" t="s">
+        <v>4350</v>
+      </c>
+      <c r="E183" s="95"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="95" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B184" s="95" t="s">
+        <v>4351</v>
+      </c>
+      <c r="C184" s="95" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D184" s="95" t="s">
+        <v>4351</v>
+      </c>
+      <c r="E184" s="95"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="95" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B185" s="95" t="s">
+        <v>4352</v>
+      </c>
+      <c r="C185" s="95" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D185" s="95" t="s">
+        <v>4352</v>
+      </c>
+      <c r="E185" s="95"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="95" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B186" s="95" t="s">
+        <v>4353</v>
+      </c>
+      <c r="C186" s="95" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D186" s="95" t="s">
+        <v>4353</v>
+      </c>
+      <c r="E186" s="95"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="95" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B187" s="95" t="s">
+        <v>4354</v>
+      </c>
+      <c r="C187" s="95" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D187" s="95" t="s">
+        <v>4354</v>
+      </c>
+      <c r="E187" s="95"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="95" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B188" s="95" t="s">
+        <v>4355</v>
+      </c>
+      <c r="C188" s="95" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D188" s="95" t="s">
+        <v>4355</v>
+      </c>
+      <c r="E188" s="95"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="95" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B189" s="95" t="s">
+        <v>4356</v>
+      </c>
+      <c r="C189" s="95" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D189" s="95" t="s">
+        <v>4356</v>
+      </c>
+      <c r="E189" s="95"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="95" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B190" s="95" t="s">
+        <v>4357</v>
+      </c>
+      <c r="C190" s="95" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D190" s="95" t="s">
+        <v>4357</v>
+      </c>
+      <c r="E190" s="95"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="95" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B191" s="95" t="s">
+        <v>4358</v>
+      </c>
+      <c r="C191" s="95" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D191" s="95" t="s">
+        <v>4358</v>
+      </c>
+      <c r="E191" s="95"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="95" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B192" s="95" t="s">
+        <v>4359</v>
+      </c>
+      <c r="C192" s="95" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D192" s="95" t="s">
+        <v>4359</v>
+      </c>
+      <c r="E192" s="95"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="95" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B193" s="95" t="s">
+        <v>4360</v>
+      </c>
+      <c r="C193" s="95" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D193" s="95" t="s">
+        <v>4360</v>
+      </c>
+      <c r="E193" s="95"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="95" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B194" s="95" t="s">
+        <v>4361</v>
+      </c>
+      <c r="C194" s="95" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D194" s="95" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E194" s="95"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="95" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B195" s="95" t="s">
+        <v>4362</v>
+      </c>
+      <c r="C195" s="95" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D195" s="95" t="s">
+        <v>4362</v>
+      </c>
+      <c r="E195" s="95"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="95" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B196" s="95" t="s">
+        <v>4363</v>
+      </c>
+      <c r="C196" s="95" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D196" s="95" t="s">
+        <v>4363</v>
+      </c>
+      <c r="E196" s="95"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="95" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B197" s="95" t="s">
+        <v>4364</v>
+      </c>
+      <c r="C197" s="95" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D197" s="95" t="s">
+        <v>4364</v>
+      </c>
+      <c r="E197" s="95"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="95" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B198" s="95" t="s">
+        <v>4365</v>
+      </c>
+      <c r="C198" s="95" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D198" s="95" t="s">
+        <v>4365</v>
+      </c>
+      <c r="E198" s="95"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="95"/>
+      <c r="B199" s="95"/>
+      <c r="C199" s="95"/>
+      <c r="D199" s="95"/>
+      <c r="E199" s="95"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="94" t="s">
+        <v>4366</v>
+      </c>
+      <c r="B200" s="94"/>
+      <c r="C200" s="95"/>
+      <c r="D200" s="95"/>
+      <c r="E200" s="95"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B201" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C201" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D201" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E201" s="95"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="95" t="s">
+        <v>480</v>
+      </c>
+      <c r="B202" s="95" t="s">
+        <v>4367</v>
+      </c>
+      <c r="C202" s="95" t="s">
+        <v>480</v>
+      </c>
+      <c r="D202" s="95" t="s">
+        <v>4367</v>
+      </c>
+      <c r="E202" s="95"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="95" t="s">
+        <v>488</v>
+      </c>
+      <c r="B203" s="95" t="s">
+        <v>4368</v>
+      </c>
+      <c r="C203" s="95" t="s">
+        <v>488</v>
+      </c>
+      <c r="D203" s="95" t="s">
+        <v>4368</v>
+      </c>
+      <c r="E203" s="95"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="95" t="s">
+        <v>494</v>
+      </c>
+      <c r="B204" s="95" t="s">
+        <v>4369</v>
+      </c>
+      <c r="C204" s="95" t="s">
+        <v>494</v>
+      </c>
+      <c r="D204" s="95" t="s">
+        <v>4369</v>
+      </c>
+      <c r="E204" s="95"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="95" t="s">
+        <v>497</v>
+      </c>
+      <c r="B205" s="95" t="s">
+        <v>4370</v>
+      </c>
+      <c r="C205" s="95" t="s">
+        <v>497</v>
+      </c>
+      <c r="D205" s="95" t="s">
+        <v>4370</v>
+      </c>
+      <c r="E205" s="95"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="95" t="s">
+        <v>499</v>
+      </c>
+      <c r="B206" s="95" t="s">
+        <v>4371</v>
+      </c>
+      <c r="C206" s="95" t="s">
+        <v>499</v>
+      </c>
+      <c r="D206" s="95" t="s">
+        <v>4371</v>
+      </c>
+      <c r="E206" s="95"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="95" t="s">
+        <v>505</v>
+      </c>
+      <c r="B207" s="95" t="s">
+        <v>4372</v>
+      </c>
+      <c r="C207" s="95" t="s">
+        <v>505</v>
+      </c>
+      <c r="D207" s="95" t="s">
+        <v>4372</v>
+      </c>
+      <c r="E207" s="95"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="95" t="s">
+        <v>510</v>
+      </c>
+      <c r="B208" s="95" t="s">
+        <v>4373</v>
+      </c>
+      <c r="C208" s="95" t="s">
+        <v>510</v>
+      </c>
+      <c r="D208" s="95" t="s">
+        <v>4373</v>
+      </c>
+      <c r="E208" s="95"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="95" t="s">
+        <v>513</v>
+      </c>
+      <c r="B209" s="95" t="s">
+        <v>4374</v>
+      </c>
+      <c r="C209" s="95" t="s">
+        <v>513</v>
+      </c>
+      <c r="D209" s="95" t="s">
+        <v>4374</v>
+      </c>
+      <c r="E209" s="95"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="95" t="s">
+        <v>516</v>
+      </c>
+      <c r="B210" s="95" t="s">
+        <v>4375</v>
+      </c>
+      <c r="C210" s="95" t="s">
+        <v>516</v>
+      </c>
+      <c r="D210" s="95" t="s">
+        <v>4375</v>
+      </c>
+      <c r="E210" s="95"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="B211" s="95" t="s">
+        <v>4376</v>
+      </c>
+      <c r="C211" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="D211" s="95" t="s">
+        <v>4376</v>
+      </c>
+      <c r="E211" s="95"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="95" t="s">
+        <v>523</v>
+      </c>
+      <c r="B212" s="95" t="s">
+        <v>4377</v>
+      </c>
+      <c r="C212" s="95" t="s">
+        <v>523</v>
+      </c>
+      <c r="D212" s="95" t="s">
+        <v>4377</v>
+      </c>
+      <c r="E212" s="95"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="95" t="s">
+        <v>526</v>
+      </c>
+      <c r="B213" s="95" t="s">
+        <v>4378</v>
+      </c>
+      <c r="C213" s="95" t="s">
+        <v>526</v>
+      </c>
+      <c r="D213" s="95" t="s">
+        <v>4378</v>
+      </c>
+      <c r="E213" s="95"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="95" t="s">
+        <v>529</v>
+      </c>
+      <c r="B214" s="95" t="s">
+        <v>4379</v>
+      </c>
+      <c r="C214" s="95" t="s">
+        <v>529</v>
+      </c>
+      <c r="D214" s="95" t="s">
+        <v>4379</v>
+      </c>
+      <c r="E214" s="95"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="95" t="s">
+        <v>532</v>
+      </c>
+      <c r="B215" s="95" t="s">
+        <v>4380</v>
+      </c>
+      <c r="C215" s="95" t="s">
+        <v>532</v>
+      </c>
+      <c r="D215" s="95" t="s">
+        <v>4380</v>
+      </c>
+      <c r="E215" s="95"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="95" t="s">
+        <v>535</v>
+      </c>
+      <c r="B216" s="95" t="s">
+        <v>4381</v>
+      </c>
+      <c r="C216" s="95" t="s">
+        <v>535</v>
+      </c>
+      <c r="D216" s="95" t="s">
+        <v>4381</v>
+      </c>
+      <c r="E216" s="95"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="95" t="s">
+        <v>538</v>
+      </c>
+      <c r="B217" s="95" t="s">
+        <v>4382</v>
+      </c>
+      <c r="C217" s="95" t="s">
+        <v>538</v>
+      </c>
+      <c r="D217" s="95" t="s">
+        <v>4382</v>
+      </c>
+      <c r="E217" s="95"/>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="95" t="s">
+        <v>541</v>
+      </c>
+      <c r="B218" s="95" t="s">
+        <v>4383</v>
+      </c>
+      <c r="C218" s="95" t="s">
+        <v>541</v>
+      </c>
+      <c r="D218" s="95" t="s">
+        <v>4383</v>
+      </c>
+      <c r="E218" s="95"/>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="95" t="s">
+        <v>546</v>
+      </c>
+      <c r="B219" s="95" t="s">
+        <v>4384</v>
+      </c>
+      <c r="C219" s="95" t="s">
+        <v>546</v>
+      </c>
+      <c r="D219" s="95" t="s">
+        <v>4384</v>
+      </c>
+      <c r="E219" s="95"/>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="95" t="s">
+        <v>550</v>
+      </c>
+      <c r="B220" s="95" t="s">
+        <v>4385</v>
+      </c>
+      <c r="C220" s="95" t="s">
+        <v>550</v>
+      </c>
+      <c r="D220" s="95" t="s">
+        <v>4385</v>
+      </c>
+      <c r="E220" s="95"/>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="95" t="s">
+        <v>553</v>
+      </c>
+      <c r="B221" s="95" t="s">
+        <v>4386</v>
+      </c>
+      <c r="C221" s="95" t="s">
+        <v>553</v>
+      </c>
+      <c r="D221" s="95" t="s">
+        <v>4386</v>
+      </c>
+      <c r="E221" s="95"/>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="95" t="s">
+        <v>556</v>
+      </c>
+      <c r="B222" s="95" t="s">
+        <v>4387</v>
+      </c>
+      <c r="C222" s="95" t="s">
+        <v>556</v>
+      </c>
+      <c r="D222" s="95" t="s">
+        <v>4387</v>
+      </c>
+      <c r="E222" s="95"/>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="95" t="s">
+        <v>559</v>
+      </c>
+      <c r="B223" s="95" t="s">
+        <v>4388</v>
+      </c>
+      <c r="C223" s="95" t="s">
+        <v>559</v>
+      </c>
+      <c r="D223" s="95" t="s">
+        <v>4388</v>
+      </c>
+      <c r="E223" s="95"/>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="95"/>
+      <c r="B224" s="95"/>
+      <c r="C224" s="95"/>
+      <c r="D224" s="95"/>
+      <c r="E224" s="95"/>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="94" t="s">
+        <v>4389</v>
+      </c>
+      <c r="B225" s="94"/>
+      <c r="C225" s="94"/>
+      <c r="D225" s="95"/>
+      <c r="E225" s="95"/>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B226" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C226" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D226" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E226" s="95"/>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="95" t="s">
+        <v>580</v>
+      </c>
+      <c r="B227" s="95" t="s">
+        <v>4390</v>
+      </c>
+      <c r="C227" s="95" t="s">
+        <v>580</v>
+      </c>
+      <c r="D227" s="95" t="s">
+        <v>4390</v>
+      </c>
+      <c r="E227" s="95"/>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="95" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B228" s="95" t="s">
+        <v>4392</v>
+      </c>
+      <c r="C228" s="95" t="s">
+        <v>4391</v>
+      </c>
+      <c r="D228" s="95" t="s">
+        <v>4392</v>
+      </c>
+      <c r="E228" s="95"/>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="95" t="s">
+        <v>591</v>
+      </c>
+      <c r="B229" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C229" s="95" t="s">
+        <v>591</v>
+      </c>
+      <c r="D229" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E229" s="95"/>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="95" t="s">
+        <v>597</v>
+      </c>
+      <c r="B230" s="95" t="s">
+        <v>4394</v>
+      </c>
+      <c r="C230" s="95" t="s">
+        <v>597</v>
+      </c>
+      <c r="D230" s="95" t="s">
+        <v>4394</v>
+      </c>
+      <c r="E230" s="95"/>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="95" t="s">
+        <v>603</v>
+      </c>
+      <c r="B231" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C231" s="95" t="s">
+        <v>603</v>
+      </c>
+      <c r="D231" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E231" s="95"/>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="95" t="s">
+        <v>611</v>
+      </c>
+      <c r="B232" s="95" t="s">
+        <v>4396</v>
+      </c>
+      <c r="C232" s="95" t="s">
+        <v>611</v>
+      </c>
+      <c r="D232" s="95" t="s">
+        <v>4396</v>
+      </c>
+      <c r="E232" s="95"/>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="95" t="s">
+        <v>614</v>
+      </c>
+      <c r="B233" s="95" t="s">
+        <v>4397</v>
+      </c>
+      <c r="C233" s="95" t="s">
+        <v>614</v>
+      </c>
+      <c r="D233" s="95" t="s">
+        <v>4397</v>
+      </c>
+      <c r="E233" s="95"/>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="95"/>
+      <c r="B234" s="95"/>
+      <c r="C234" s="95"/>
+      <c r="D234" s="95"/>
+      <c r="E234" s="95"/>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="94" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B235" s="94"/>
+      <c r="C235" s="95"/>
+      <c r="D235" s="95"/>
+      <c r="E235" s="95"/>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B236" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C236" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D236" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E236" s="95"/>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="97" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B237" s="95"/>
+      <c r="C237" s="95"/>
+      <c r="D237" s="95"/>
+      <c r="E237" s="95"/>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="95" t="s">
+        <v>421</v>
+      </c>
+      <c r="B238" s="95" t="s">
+        <v>4400</v>
+      </c>
+      <c r="C238" s="95" t="s">
+        <v>421</v>
+      </c>
+      <c r="D238" s="95" t="s">
+        <v>4400</v>
+      </c>
+      <c r="E238" s="95"/>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="95" t="s">
+        <v>425</v>
+      </c>
+      <c r="B239" s="95" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C239" s="95" t="s">
+        <v>425</v>
+      </c>
+      <c r="D239" s="95" t="s">
+        <v>4401</v>
+      </c>
+      <c r="E239" s="95"/>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="95" t="s">
+        <v>427</v>
+      </c>
+      <c r="B240" s="95" t="s">
+        <v>4402</v>
+      </c>
+      <c r="C240" s="95" t="s">
+        <v>427</v>
+      </c>
+      <c r="D240" s="95" t="s">
+        <v>4402</v>
+      </c>
+      <c r="E240" s="95"/>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="95" t="s">
+        <v>429</v>
+      </c>
+      <c r="B241" s="95" t="s">
+        <v>4403</v>
+      </c>
+      <c r="C241" s="95" t="s">
+        <v>429</v>
+      </c>
+      <c r="D241" s="95" t="s">
+        <v>4403</v>
+      </c>
+      <c r="E241" s="95"/>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="95" t="s">
+        <v>431</v>
+      </c>
+      <c r="B242" s="95" t="s">
+        <v>4404</v>
+      </c>
+      <c r="C242" s="95" t="s">
+        <v>431</v>
+      </c>
+      <c r="D242" s="95" t="s">
+        <v>4404</v>
+      </c>
+      <c r="E242" s="95"/>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="95" t="s">
+        <v>434</v>
+      </c>
+      <c r="B243" s="95" t="s">
+        <v>4405</v>
+      </c>
+      <c r="C243" s="95" t="s">
+        <v>434</v>
+      </c>
+      <c r="D243" s="95" t="s">
+        <v>4405</v>
+      </c>
+      <c r="E243" s="95"/>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="95" t="s">
+        <v>436</v>
+      </c>
+      <c r="B244" s="95" t="s">
+        <v>4406</v>
+      </c>
+      <c r="C244" s="95" t="s">
+        <v>436</v>
+      </c>
+      <c r="D244" s="95" t="s">
+        <v>4406</v>
+      </c>
+      <c r="E244" s="95"/>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="95" t="s">
+        <v>439</v>
+      </c>
+      <c r="B245" s="95" t="s">
+        <v>4407</v>
+      </c>
+      <c r="C245" s="95" t="s">
+        <v>439</v>
+      </c>
+      <c r="D245" s="95" t="s">
+        <v>4407</v>
+      </c>
+      <c r="E245" s="95"/>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="95" t="s">
+        <v>444</v>
+      </c>
+      <c r="B246" s="95" t="s">
+        <v>4408</v>
+      </c>
+      <c r="C246" s="95" t="s">
+        <v>444</v>
+      </c>
+      <c r="D246" s="95" t="s">
+        <v>4408</v>
+      </c>
+      <c r="E246" s="95"/>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="95" t="s">
+        <v>446</v>
+      </c>
+      <c r="B247" s="95" t="s">
+        <v>4409</v>
+      </c>
+      <c r="C247" s="95" t="s">
+        <v>446</v>
+      </c>
+      <c r="D247" s="95" t="s">
+        <v>4409</v>
+      </c>
+      <c r="E247" s="95"/>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="95" t="s">
+        <v>448</v>
+      </c>
+      <c r="B248" s="95" t="s">
+        <v>4410</v>
+      </c>
+      <c r="C248" s="95" t="s">
+        <v>448</v>
+      </c>
+      <c r="D248" s="95" t="s">
+        <v>4410</v>
+      </c>
+      <c r="E248" s="95"/>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="95" t="s">
+        <v>450</v>
+      </c>
+      <c r="B249" s="95" t="s">
+        <v>4411</v>
+      </c>
+      <c r="C249" s="95" t="s">
+        <v>450</v>
+      </c>
+      <c r="D249" s="95" t="s">
+        <v>4411</v>
+      </c>
+      <c r="E249" s="95"/>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="95" t="s">
+        <v>452</v>
+      </c>
+      <c r="B250" s="95" t="s">
+        <v>4412</v>
+      </c>
+      <c r="C250" s="95" t="s">
+        <v>452</v>
+      </c>
+      <c r="D250" s="95" t="s">
+        <v>4412</v>
+      </c>
+      <c r="E250" s="95"/>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="95" t="s">
+        <v>454</v>
+      </c>
+      <c r="B251" s="95" t="s">
+        <v>4413</v>
+      </c>
+      <c r="C251" s="95" t="s">
+        <v>454</v>
+      </c>
+      <c r="D251" s="95" t="s">
+        <v>4413</v>
+      </c>
+      <c r="E251" s="95"/>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="95" t="s">
+        <v>456</v>
+      </c>
+      <c r="B252" s="95" t="s">
+        <v>4414</v>
+      </c>
+      <c r="C252" s="95" t="s">
+        <v>456</v>
+      </c>
+      <c r="D252" s="95" t="s">
+        <v>4414</v>
+      </c>
+      <c r="E252" s="95"/>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="95" t="s">
+        <v>458</v>
+      </c>
+      <c r="B253" s="95" t="s">
+        <v>4415</v>
+      </c>
+      <c r="C253" s="95" t="s">
+        <v>458</v>
+      </c>
+      <c r="D253" s="95" t="s">
+        <v>4415</v>
+      </c>
+      <c r="E253" s="95"/>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="95" t="s">
+        <v>460</v>
+      </c>
+      <c r="B254" s="95" t="s">
+        <v>4416</v>
+      </c>
+      <c r="C254" s="95" t="s">
+        <v>460</v>
+      </c>
+      <c r="D254" s="95" t="s">
+        <v>4416</v>
+      </c>
+      <c r="E254" s="95"/>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="95" t="s">
+        <v>462</v>
+      </c>
+      <c r="B255" s="95" t="s">
+        <v>4417</v>
+      </c>
+      <c r="C255" s="95" t="s">
+        <v>462</v>
+      </c>
+      <c r="D255" s="95" t="s">
+        <v>4417</v>
+      </c>
+      <c r="E255" s="95"/>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="B256" s="95" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C256" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="D256" s="95" t="s">
+        <v>4418</v>
+      </c>
+      <c r="E256" s="95"/>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="95" t="s">
+        <v>466</v>
+      </c>
+      <c r="B257" s="95" t="s">
+        <v>4419</v>
+      </c>
+      <c r="C257" s="95" t="s">
+        <v>466</v>
+      </c>
+      <c r="D257" s="95" t="s">
+        <v>4419</v>
+      </c>
+      <c r="E257" s="95"/>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="95" t="s">
+        <v>468</v>
+      </c>
+      <c r="B258" s="95" t="s">
+        <v>4420</v>
+      </c>
+      <c r="C258" s="95" t="s">
+        <v>468</v>
+      </c>
+      <c r="D258" s="95" t="s">
+        <v>4420</v>
+      </c>
+      <c r="E258" s="95"/>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="95" t="s">
+        <v>470</v>
+      </c>
+      <c r="B259" s="95" t="s">
+        <v>4421</v>
+      </c>
+      <c r="C259" s="95" t="s">
+        <v>470</v>
+      </c>
+      <c r="D259" s="95" t="s">
+        <v>4421</v>
+      </c>
+      <c r="E259" s="95"/>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="95" t="s">
+        <v>472</v>
+      </c>
+      <c r="B260" s="95" t="s">
+        <v>4422</v>
+      </c>
+      <c r="C260" s="95" t="s">
+        <v>472</v>
+      </c>
+      <c r="D260" s="95" t="s">
+        <v>4422</v>
+      </c>
+      <c r="E260" s="95"/>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="97" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B261" s="95"/>
+      <c r="C261" s="95"/>
+      <c r="D261" s="95"/>
+      <c r="E261" s="95"/>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="95" t="s">
+        <v>621</v>
+      </c>
+      <c r="B262" s="95" t="s">
+        <v>4424</v>
+      </c>
+      <c r="C262" s="95" t="s">
+        <v>621</v>
+      </c>
+      <c r="D262" s="95" t="s">
+        <v>4424</v>
+      </c>
+      <c r="E262" s="95"/>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="95" t="s">
+        <v>625</v>
+      </c>
+      <c r="B263" s="95" t="s">
+        <v>4425</v>
+      </c>
+      <c r="C263" s="95" t="s">
+        <v>625</v>
+      </c>
+      <c r="D263" s="95" t="s">
+        <v>4425</v>
+      </c>
+      <c r="E263" s="95"/>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="95" t="s">
+        <v>631</v>
+      </c>
+      <c r="B264" s="95" t="s">
+        <v>4426</v>
+      </c>
+      <c r="C264" s="95" t="s">
+        <v>631</v>
+      </c>
+      <c r="D264" s="95" t="s">
+        <v>4426</v>
+      </c>
+      <c r="E264" s="95"/>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="95" t="s">
+        <v>636</v>
+      </c>
+      <c r="B265" s="95" t="s">
+        <v>4427</v>
+      </c>
+      <c r="C265" s="95" t="s">
+        <v>636</v>
+      </c>
+      <c r="D265" s="95" t="s">
+        <v>4427</v>
+      </c>
+      <c r="E265" s="95"/>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="B266" s="95" t="s">
+        <v>4428</v>
+      </c>
+      <c r="C266" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="D266" s="95" t="s">
+        <v>4428</v>
+      </c>
+      <c r="E266" s="95"/>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="95" t="s">
+        <v>651</v>
+      </c>
+      <c r="B267" s="95" t="s">
+        <v>4429</v>
+      </c>
+      <c r="C267" s="95" t="s">
+        <v>651</v>
+      </c>
+      <c r="D267" s="95" t="s">
+        <v>4429</v>
+      </c>
+      <c r="E267" s="95"/>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="95" t="s">
+        <v>655</v>
+      </c>
+      <c r="B268" s="95" t="s">
+        <v>4430</v>
+      </c>
+      <c r="C268" s="95" t="s">
+        <v>655</v>
+      </c>
+      <c r="D268" s="95" t="s">
+        <v>4430</v>
+      </c>
+      <c r="E268" s="95"/>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="95" t="s">
+        <v>658</v>
+      </c>
+      <c r="B269" s="95" t="s">
+        <v>4431</v>
+      </c>
+      <c r="C269" s="95" t="s">
+        <v>658</v>
+      </c>
+      <c r="D269" s="95" t="s">
+        <v>4431</v>
+      </c>
+      <c r="E269" s="95"/>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="95" t="s">
+        <v>662</v>
+      </c>
+      <c r="B270" s="95" t="s">
+        <v>4432</v>
+      </c>
+      <c r="C270" s="95" t="s">
+        <v>662</v>
+      </c>
+      <c r="D270" s="95" t="s">
+        <v>4432</v>
+      </c>
+      <c r="E270" s="95"/>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="97" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B271" s="95"/>
+      <c r="C271" s="95"/>
+      <c r="D271" s="95"/>
+      <c r="E271" s="95"/>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="95" t="s">
+        <v>664</v>
+      </c>
+      <c r="B272" s="95" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C272" s="95" t="s">
+        <v>664</v>
+      </c>
+      <c r="D272" s="95" t="s">
+        <v>4434</v>
+      </c>
+      <c r="E272" s="95"/>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="95" t="s">
+        <v>666</v>
+      </c>
+      <c r="B273" s="95" t="s">
+        <v>4435</v>
+      </c>
+      <c r="C273" s="95" t="s">
+        <v>666</v>
+      </c>
+      <c r="D273" s="95" t="s">
+        <v>4435</v>
+      </c>
+      <c r="E273" s="95"/>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="95" t="s">
+        <v>671</v>
+      </c>
+      <c r="B274" s="95" t="s">
+        <v>4436</v>
+      </c>
+      <c r="C274" s="95" t="s">
+        <v>671</v>
+      </c>
+      <c r="D274" s="95" t="s">
+        <v>4436</v>
+      </c>
+      <c r="E274" s="95"/>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="95" t="s">
+        <v>674</v>
+      </c>
+      <c r="B275" s="95" t="s">
+        <v>4437</v>
+      </c>
+      <c r="C275" s="95" t="s">
+        <v>674</v>
+      </c>
+      <c r="D275" s="95" t="s">
+        <v>4437</v>
+      </c>
+      <c r="E275" s="95"/>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="95" t="s">
+        <v>677</v>
+      </c>
+      <c r="B276" s="95" t="s">
+        <v>4438</v>
+      </c>
+      <c r="C276" s="95" t="s">
+        <v>677</v>
+      </c>
+      <c r="D276" s="95" t="s">
+        <v>4438</v>
+      </c>
+      <c r="E276" s="95"/>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="95" t="s">
+        <v>680</v>
+      </c>
+      <c r="B277" s="95" t="s">
+        <v>4439</v>
+      </c>
+      <c r="C277" s="95" t="s">
+        <v>680</v>
+      </c>
+      <c r="D277" s="95" t="s">
+        <v>4439</v>
+      </c>
+      <c r="E277" s="95"/>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="95" t="s">
+        <v>682</v>
+      </c>
+      <c r="B278" s="95" t="s">
+        <v>4440</v>
+      </c>
+      <c r="C278" s="95" t="s">
+        <v>682</v>
+      </c>
+      <c r="D278" s="95" t="s">
+        <v>4440</v>
+      </c>
+      <c r="E278" s="95"/>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="95" t="s">
+        <v>684</v>
+      </c>
+      <c r="B279" s="95" t="s">
+        <v>4441</v>
+      </c>
+      <c r="C279" s="95" t="s">
+        <v>684</v>
+      </c>
+      <c r="D279" s="95" t="s">
+        <v>4441</v>
+      </c>
+      <c r="E279" s="95"/>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="95" t="s">
+        <v>686</v>
+      </c>
+      <c r="B280" s="95" t="s">
+        <v>4442</v>
+      </c>
+      <c r="C280" s="95" t="s">
+        <v>686</v>
+      </c>
+      <c r="D280" s="95" t="s">
+        <v>4442</v>
+      </c>
+      <c r="E280" s="95"/>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="97" t="s">
+        <v>4443</v>
+      </c>
+      <c r="B281" s="95"/>
+      <c r="C281" s="95"/>
+      <c r="D281" s="95"/>
+      <c r="E281" s="95"/>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="95" t="s">
+        <v>689</v>
+      </c>
+      <c r="B282" s="95" t="s">
+        <v>4444</v>
+      </c>
+      <c r="C282" s="95" t="s">
+        <v>689</v>
+      </c>
+      <c r="D282" s="95" t="s">
+        <v>4444</v>
+      </c>
+      <c r="E282" s="95"/>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="95" t="s">
+        <v>697</v>
+      </c>
+      <c r="B283" s="95" t="s">
+        <v>4445</v>
+      </c>
+      <c r="C283" s="95" t="s">
+        <v>697</v>
+      </c>
+      <c r="D283" s="95" t="s">
+        <v>4445</v>
+      </c>
+      <c r="E283" s="95"/>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="95" t="s">
+        <v>4446</v>
+      </c>
+      <c r="B284" s="95" t="s">
+        <v>4447</v>
+      </c>
+      <c r="C284" s="95" t="s">
+        <v>4446</v>
+      </c>
+      <c r="D284" s="95" t="s">
+        <v>4447</v>
+      </c>
+      <c r="E284" s="95"/>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="95" t="s">
+        <v>706</v>
+      </c>
+      <c r="B285" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C285" s="95" t="s">
+        <v>706</v>
+      </c>
+      <c r="D285" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E285" s="95"/>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="95" t="s">
+        <v>709</v>
+      </c>
+      <c r="B286" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C286" s="95" t="s">
+        <v>709</v>
+      </c>
+      <c r="D286" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E286" s="95"/>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="95" t="s">
+        <v>715</v>
+      </c>
+      <c r="B287" s="95" t="s">
+        <v>4394</v>
+      </c>
+      <c r="C287" s="95" t="s">
+        <v>715</v>
+      </c>
+      <c r="D287" s="95" t="s">
+        <v>4394</v>
+      </c>
+      <c r="E287" s="95"/>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="95" t="s">
+        <v>721</v>
+      </c>
+      <c r="B288" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C288" s="95" t="s">
+        <v>721</v>
+      </c>
+      <c r="D288" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E288" s="95"/>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="95" t="s">
+        <v>725</v>
+      </c>
+      <c r="B289" s="95" t="s">
+        <v>4449</v>
+      </c>
+      <c r="C289" s="95" t="s">
+        <v>725</v>
+      </c>
+      <c r="D289" s="95" t="s">
+        <v>4449</v>
+      </c>
+      <c r="E289" s="95"/>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="95" t="s">
+        <v>728</v>
+      </c>
+      <c r="B290" s="95" t="s">
+        <v>4450</v>
+      </c>
+      <c r="C290" s="95" t="s">
+        <v>728</v>
+      </c>
+      <c r="D290" s="95" t="s">
+        <v>4450</v>
+      </c>
+      <c r="E290" s="95"/>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="B291" s="95" t="s">
+        <v>4451</v>
+      </c>
+      <c r="C291" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="D291" s="95" t="s">
+        <v>4451</v>
+      </c>
+      <c r="E291" s="95"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="95" t="s">
+        <v>735</v>
+      </c>
+      <c r="B292" s="95" t="s">
+        <v>4452</v>
+      </c>
+      <c r="C292" s="95" t="s">
+        <v>735</v>
+      </c>
+      <c r="D292" s="95" t="s">
+        <v>4452</v>
+      </c>
+      <c r="E292" s="95"/>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="95" t="s">
+        <v>737</v>
+      </c>
+      <c r="B293" s="95" t="s">
+        <v>4453</v>
+      </c>
+      <c r="C293" s="95" t="s">
+        <v>737</v>
+      </c>
+      <c r="D293" s="95" t="s">
+        <v>4453</v>
+      </c>
+      <c r="E293" s="95"/>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="95" t="s">
+        <v>741</v>
+      </c>
+      <c r="B294" s="95" t="s">
+        <v>4454</v>
+      </c>
+      <c r="C294" s="95" t="s">
+        <v>741</v>
+      </c>
+      <c r="D294" s="95" t="s">
+        <v>4454</v>
+      </c>
+      <c r="E294" s="95"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="95" t="s">
+        <v>746</v>
+      </c>
+      <c r="B295" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C295" s="95" t="s">
+        <v>746</v>
+      </c>
+      <c r="D295" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E295" s="95"/>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="95" t="s">
+        <v>749</v>
+      </c>
+      <c r="B296" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C296" s="95" t="s">
+        <v>749</v>
+      </c>
+      <c r="D296" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E296" s="95"/>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="95" t="s">
+        <v>752</v>
+      </c>
+      <c r="B297" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C297" s="95" t="s">
+        <v>752</v>
+      </c>
+      <c r="D297" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E297" s="95"/>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="95" t="s">
+        <v>756</v>
+      </c>
+      <c r="B298" s="95" t="s">
+        <v>4455</v>
+      </c>
+      <c r="C298" s="95" t="s">
+        <v>756</v>
+      </c>
+      <c r="D298" s="95" t="s">
+        <v>4455</v>
+      </c>
+      <c r="E298" s="95"/>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="95" t="s">
+        <v>762</v>
+      </c>
+      <c r="B299" s="95" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C299" s="95" t="s">
+        <v>762</v>
+      </c>
+      <c r="D299" s="95" t="s">
+        <v>4456</v>
+      </c>
+      <c r="E299" s="95"/>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="95" t="s">
+        <v>767</v>
+      </c>
+      <c r="B300" s="95" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C300" s="95" t="s">
+        <v>767</v>
+      </c>
+      <c r="D300" s="95" t="s">
+        <v>4457</v>
+      </c>
+      <c r="E300" s="95"/>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="95" t="s">
+        <v>769</v>
+      </c>
+      <c r="B301" s="95" t="s">
+        <v>4458</v>
+      </c>
+      <c r="C301" s="95" t="s">
+        <v>769</v>
+      </c>
+      <c r="D301" s="95" t="s">
+        <v>4458</v>
+      </c>
+      <c r="E301" s="95"/>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="97" t="s">
+        <v>4459</v>
+      </c>
+      <c r="B302" s="95"/>
+      <c r="C302" s="95"/>
+      <c r="D302" s="95"/>
+      <c r="E302" s="95"/>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="95" t="s">
+        <v>772</v>
+      </c>
+      <c r="B303" s="95" t="s">
+        <v>4460</v>
+      </c>
+      <c r="C303" s="95" t="s">
+        <v>772</v>
+      </c>
+      <c r="D303" s="95" t="s">
+        <v>4460</v>
+      </c>
+      <c r="E303" s="95"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="95" t="s">
+        <v>774</v>
+      </c>
+      <c r="B304" s="95" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C304" s="95" t="s">
+        <v>774</v>
+      </c>
+      <c r="D304" s="95" t="s">
+        <v>4461</v>
+      </c>
+      <c r="E304" s="95"/>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="B305" s="95" t="s">
+        <v>4462</v>
+      </c>
+      <c r="C305" s="95" t="s">
+        <v>777</v>
+      </c>
+      <c r="D305" s="95" t="s">
+        <v>4462</v>
+      </c>
+      <c r="E305" s="95"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="95" t="s">
+        <v>790</v>
+      </c>
+      <c r="B306" s="95" t="s">
+        <v>4463</v>
+      </c>
+      <c r="C306" s="95" t="s">
+        <v>790</v>
+      </c>
+      <c r="D306" s="95" t="s">
+        <v>4463</v>
+      </c>
+      <c r="E306" s="95"/>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="95" t="s">
+        <v>794</v>
+      </c>
+      <c r="B307" s="95" t="s">
+        <v>4464</v>
+      </c>
+      <c r="C307" s="95" t="s">
+        <v>794</v>
+      </c>
+      <c r="D307" s="95" t="s">
+        <v>4464</v>
+      </c>
+      <c r="E307" s="95"/>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="95" t="s">
+        <v>801</v>
+      </c>
+      <c r="B308" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C308" s="95" t="s">
+        <v>801</v>
+      </c>
+      <c r="D308" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E308" s="95"/>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="97" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B309" s="97"/>
+      <c r="C309" s="95"/>
+      <c r="D309" s="95"/>
+      <c r="E309" s="95"/>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="95" t="s">
+        <v>809</v>
+      </c>
+      <c r="B310" s="95" t="s">
+        <v>4466</v>
+      </c>
+      <c r="C310" s="95" t="s">
+        <v>809</v>
+      </c>
+      <c r="D310" s="95" t="s">
+        <v>4466</v>
+      </c>
+      <c r="E310" s="95"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="95" t="s">
+        <v>813</v>
+      </c>
+      <c r="B311" s="95" t="s">
+        <v>4467</v>
+      </c>
+      <c r="C311" s="95" t="s">
+        <v>813</v>
+      </c>
+      <c r="D311" s="95" t="s">
+        <v>4467</v>
+      </c>
+      <c r="E311" s="95"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="95" t="s">
+        <v>818</v>
+      </c>
+      <c r="B312" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C312" s="95" t="s">
+        <v>818</v>
+      </c>
+      <c r="D312" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E312" s="95"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="95" t="s">
+        <v>821</v>
+      </c>
+      <c r="B313" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C313" s="95" t="s">
+        <v>821</v>
+      </c>
+      <c r="D313" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E313" s="95"/>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="95" t="s">
+        <v>824</v>
+      </c>
+      <c r="B314" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C314" s="95" t="s">
+        <v>824</v>
+      </c>
+      <c r="D314" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E314" s="95"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="95" t="s">
+        <v>827</v>
+      </c>
+      <c r="B315" s="95" t="s">
+        <v>4468</v>
+      </c>
+      <c r="C315" s="95" t="s">
+        <v>827</v>
+      </c>
+      <c r="D315" s="95" t="s">
+        <v>4468</v>
+      </c>
+      <c r="E315" s="95"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="95" t="s">
+        <v>835</v>
+      </c>
+      <c r="B316" s="95" t="s">
+        <v>4469</v>
+      </c>
+      <c r="C316" s="95" t="s">
+        <v>835</v>
+      </c>
+      <c r="D316" s="95" t="s">
+        <v>4469</v>
+      </c>
+      <c r="E316" s="95"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="95" t="s">
+        <v>840</v>
+      </c>
+      <c r="B317" s="95" t="s">
+        <v>4470</v>
+      </c>
+      <c r="C317" s="95" t="s">
+        <v>840</v>
+      </c>
+      <c r="D317" s="95" t="s">
+        <v>4470</v>
+      </c>
+      <c r="E317" s="95"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="95" t="s">
+        <v>845</v>
+      </c>
+      <c r="B318" s="95" t="s">
+        <v>4471</v>
+      </c>
+      <c r="C318" s="95" t="s">
+        <v>845</v>
+      </c>
+      <c r="D318" s="95" t="s">
+        <v>4471</v>
+      </c>
+      <c r="E318" s="95"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="95" t="s">
+        <v>848</v>
+      </c>
+      <c r="B319" s="95" t="s">
+        <v>4472</v>
+      </c>
+      <c r="C319" s="95" t="s">
+        <v>848</v>
+      </c>
+      <c r="D319" s="95" t="s">
+        <v>4472</v>
+      </c>
+      <c r="E319" s="95"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="95" t="s">
+        <v>852</v>
+      </c>
+      <c r="B320" s="95" t="s">
+        <v>4473</v>
+      </c>
+      <c r="C320" s="95" t="s">
+        <v>852</v>
+      </c>
+      <c r="D320" s="95" t="s">
+        <v>4473</v>
+      </c>
+      <c r="E320" s="95"/>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="95" t="s">
+        <v>855</v>
+      </c>
+      <c r="B321" s="95" t="s">
+        <v>4474</v>
+      </c>
+      <c r="C321" s="95" t="s">
+        <v>855</v>
+      </c>
+      <c r="D321" s="95" t="s">
+        <v>4474</v>
+      </c>
+      <c r="E321" s="95"/>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="95" t="s">
+        <v>857</v>
+      </c>
+      <c r="B322" s="95" t="s">
+        <v>4475</v>
+      </c>
+      <c r="C322" s="95" t="s">
+        <v>857</v>
+      </c>
+      <c r="D322" s="95" t="s">
+        <v>4475</v>
+      </c>
+      <c r="E322" s="95"/>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="95" t="s">
+        <v>859</v>
+      </c>
+      <c r="B323" s="95" t="s">
+        <v>4476</v>
+      </c>
+      <c r="C323" s="95" t="s">
+        <v>859</v>
+      </c>
+      <c r="D323" s="95" t="s">
+        <v>4476</v>
+      </c>
+      <c r="E323" s="95"/>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="95" t="s">
+        <v>864</v>
+      </c>
+      <c r="B324" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C324" s="95" t="s">
+        <v>864</v>
+      </c>
+      <c r="D324" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E324" s="95"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="95" t="s">
+        <v>867</v>
+      </c>
+      <c r="B325" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C325" s="95" t="s">
+        <v>867</v>
+      </c>
+      <c r="D325" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E325" s="95"/>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="95" t="s">
+        <v>870</v>
+      </c>
+      <c r="B326" s="95" t="s">
+        <v>4477</v>
+      </c>
+      <c r="C326" s="95" t="s">
+        <v>870</v>
+      </c>
+      <c r="D326" s="95" t="s">
+        <v>4477</v>
+      </c>
+      <c r="E326" s="95"/>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="95" t="s">
+        <v>873</v>
+      </c>
+      <c r="B327" s="95" t="s">
+        <v>4478</v>
+      </c>
+      <c r="C327" s="95" t="s">
+        <v>873</v>
+      </c>
+      <c r="D327" s="95" t="s">
+        <v>4478</v>
+      </c>
+      <c r="E327" s="95"/>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="95" t="s">
+        <v>876</v>
+      </c>
+      <c r="B328" s="95" t="s">
+        <v>4479</v>
+      </c>
+      <c r="C328" s="95" t="s">
+        <v>876</v>
+      </c>
+      <c r="D328" s="95" t="s">
+        <v>4479</v>
+      </c>
+      <c r="E328" s="95"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="95" t="s">
+        <v>879</v>
+      </c>
+      <c r="B329" s="95" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C329" s="95" t="s">
+        <v>879</v>
+      </c>
+      <c r="D329" s="95" t="s">
+        <v>4480</v>
+      </c>
+      <c r="E329" s="95"/>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="97" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B330" s="95"/>
+      <c r="C330" s="95"/>
+      <c r="D330" s="95"/>
+      <c r="E330" s="95"/>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="95" t="s">
+        <v>884</v>
+      </c>
+      <c r="B331" s="95" t="s">
+        <v>4482</v>
+      </c>
+      <c r="C331" s="95" t="s">
+        <v>884</v>
+      </c>
+      <c r="D331" s="95" t="s">
+        <v>4482</v>
+      </c>
+      <c r="E331" s="95"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="95" t="s">
+        <v>886</v>
+      </c>
+      <c r="B332" s="95" t="s">
+        <v>4483</v>
+      </c>
+      <c r="C332" s="95" t="s">
+        <v>886</v>
+      </c>
+      <c r="D332" s="95" t="s">
+        <v>4483</v>
+      </c>
+      <c r="E332" s="95"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="95" t="s">
+        <v>4484</v>
+      </c>
+      <c r="B333" s="95" t="s">
+        <v>4485</v>
+      </c>
+      <c r="C333" s="95" t="s">
+        <v>4484</v>
+      </c>
+      <c r="D333" s="95" t="s">
+        <v>4485</v>
+      </c>
+      <c r="E333" s="95"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="95" t="s">
+        <v>898</v>
+      </c>
+      <c r="B334" s="95" t="s">
+        <v>4464</v>
+      </c>
+      <c r="C334" s="95" t="s">
+        <v>898</v>
+      </c>
+      <c r="D334" s="95" t="s">
+        <v>4464</v>
+      </c>
+      <c r="E334" s="95"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="95" t="s">
+        <v>905</v>
+      </c>
+      <c r="B335" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C335" s="95" t="s">
+        <v>905</v>
+      </c>
+      <c r="D335" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E335" s="95"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="95" t="s">
+        <v>911</v>
+      </c>
+      <c r="B336" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C336" s="95" t="s">
+        <v>911</v>
+      </c>
+      <c r="D336" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E336" s="95"/>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="95" t="s">
+        <v>915</v>
+      </c>
+      <c r="B337" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C337" s="95" t="s">
+        <v>915</v>
+      </c>
+      <c r="D337" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E337" s="95"/>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="95" t="s">
+        <v>919</v>
+      </c>
+      <c r="B338" s="95" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C338" s="95" t="s">
+        <v>919</v>
+      </c>
+      <c r="D338" s="95" t="s">
+        <v>4486</v>
+      </c>
+      <c r="E338" s="95"/>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="95" t="s">
+        <v>925</v>
+      </c>
+      <c r="B339" s="95" t="s">
+        <v>4487</v>
+      </c>
+      <c r="C339" s="95" t="s">
+        <v>925</v>
+      </c>
+      <c r="D339" s="95" t="s">
+        <v>4487</v>
+      </c>
+      <c r="E339" s="95"/>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="95" t="s">
+        <v>931</v>
+      </c>
+      <c r="B340" s="95" t="s">
+        <v>4488</v>
+      </c>
+      <c r="C340" s="95" t="s">
+        <v>931</v>
+      </c>
+      <c r="D340" s="95" t="s">
+        <v>4488</v>
+      </c>
+      <c r="E340" s="95"/>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="95" t="s">
+        <v>936</v>
+      </c>
+      <c r="B341" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="C341" s="95" t="s">
+        <v>936</v>
+      </c>
+      <c r="D341" s="95" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E341" s="95"/>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="95" t="s">
+        <v>939</v>
+      </c>
+      <c r="B342" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="C342" s="95" t="s">
+        <v>939</v>
+      </c>
+      <c r="D342" s="95" t="s">
+        <v>4393</v>
+      </c>
+      <c r="E342" s="95"/>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="95" t="s">
+        <v>943</v>
+      </c>
+      <c r="B343" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="C343" s="95" t="s">
+        <v>943</v>
+      </c>
+      <c r="D343" s="95" t="s">
+        <v>4448</v>
+      </c>
+      <c r="E343" s="95"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="95" t="s">
+        <v>947</v>
+      </c>
+      <c r="B344" s="95" t="s">
+        <v>4489</v>
+      </c>
+      <c r="C344" s="95" t="s">
+        <v>947</v>
+      </c>
+      <c r="D344" s="95" t="s">
+        <v>4489</v>
+      </c>
+      <c r="E344" s="95"/>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="95" t="s">
+        <v>949</v>
+      </c>
+      <c r="B345" s="95" t="s">
+        <v>4490</v>
+      </c>
+      <c r="C345" s="95"/>
+      <c r="D345" s="95"/>
+      <c r="E345" s="95"/>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="95"/>
+      <c r="B346" s="95"/>
+      <c r="C346" s="95"/>
+      <c r="D346" s="95"/>
+      <c r="E346" s="95"/>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="94" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B347" s="94"/>
+      <c r="C347" s="94"/>
+      <c r="D347" s="95"/>
+      <c r="E347" s="95"/>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B348" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C348" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D348" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E348" s="95"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="97" t="s">
+        <v>4492</v>
+      </c>
+      <c r="B349" s="97"/>
+      <c r="C349" s="95"/>
+      <c r="D349" s="95"/>
+      <c r="E349" s="95"/>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="95" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B350" s="95" t="s">
+        <v>4493</v>
+      </c>
+      <c r="C350" s="95" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D350" s="95" t="s">
+        <v>4493</v>
+      </c>
+      <c r="E350" s="95"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="95" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B351" s="95" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C351" s="95" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D351" s="95" t="s">
+        <v>4494</v>
+      </c>
+      <c r="E351" s="95"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="95" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B352" s="95" t="s">
+        <v>4495</v>
+      </c>
+      <c r="C352" s="95" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D352" s="95" t="s">
+        <v>4495</v>
+      </c>
+      <c r="E352" s="95"/>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="95" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B353" s="95" t="s">
+        <v>4496</v>
+      </c>
+      <c r="C353" s="95" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D353" s="95" t="s">
+        <v>4496</v>
+      </c>
+      <c r="E353" s="95"/>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="95" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B354" s="95" t="s">
+        <v>4497</v>
+      </c>
+      <c r="C354" s="95" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D354" s="95" t="s">
+        <v>4497</v>
+      </c>
+      <c r="E354" s="95"/>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="95" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B355" s="95" t="s">
+        <v>4498</v>
+      </c>
+      <c r="C355" s="95" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D355" s="95" t="s">
+        <v>4498</v>
+      </c>
+      <c r="E355" s="95"/>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="95" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B356" s="95" t="s">
+        <v>4499</v>
+      </c>
+      <c r="C356" s="95" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D356" s="95" t="s">
+        <v>4499</v>
+      </c>
+      <c r="E356" s="95"/>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="97" t="s">
+        <v>4500</v>
+      </c>
+      <c r="B357" s="95"/>
+      <c r="C357" s="95"/>
+      <c r="D357" s="95"/>
+      <c r="E357" s="95"/>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="95" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B358" s="95" t="s">
+        <v>4501</v>
+      </c>
+      <c r="C358" s="95" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D358" s="95" t="s">
+        <v>4501</v>
+      </c>
+      <c r="E358" s="95"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="95" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B359" s="95" t="s">
+        <v>4502</v>
+      </c>
+      <c r="C359" s="95" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D359" s="95" t="s">
+        <v>4502</v>
+      </c>
+      <c r="E359" s="95"/>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="95" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B360" s="95" t="s">
+        <v>4503</v>
+      </c>
+      <c r="C360" s="95" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D360" s="95" t="s">
+        <v>4503</v>
+      </c>
+      <c r="E360" s="95"/>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="95" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B361" s="95" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C361" s="95" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D361" s="95" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E361" s="95"/>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="95" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B362" s="95" t="s">
+        <v>4505</v>
+      </c>
+      <c r="C362" s="95" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D362" s="95" t="s">
+        <v>4505</v>
+      </c>
+      <c r="E362" s="95"/>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="95" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B363" s="95" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C363" s="95" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D363" s="95" t="s">
+        <v>4506</v>
+      </c>
+      <c r="E363" s="95"/>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="95" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B364" s="95" t="s">
+        <v>4507</v>
+      </c>
+      <c r="C364" s="95" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D364" s="95" t="s">
+        <v>4507</v>
+      </c>
+      <c r="E364" s="95"/>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="95" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B365" s="95" t="s">
+        <v>4508</v>
+      </c>
+      <c r="C365" s="95" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D365" s="95" t="s">
+        <v>4508</v>
+      </c>
+      <c r="E365" s="95"/>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="95" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B366" s="95" t="s">
+        <v>4509</v>
+      </c>
+      <c r="C366" s="95" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D366" s="95" t="s">
+        <v>4509</v>
+      </c>
+      <c r="E366" s="95"/>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="97" t="s">
+        <v>4510</v>
+      </c>
+      <c r="B367" s="97"/>
+      <c r="C367" s="95"/>
+      <c r="D367" s="95"/>
+      <c r="E367" s="95"/>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="95" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B368" s="95" t="s">
+        <v>4511</v>
+      </c>
+      <c r="C368" s="95" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D368" s="95" t="s">
+        <v>4511</v>
+      </c>
+      <c r="E368" s="95"/>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="95" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B369" s="95" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C369" s="95" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D369" s="95" t="s">
+        <v>4512</v>
+      </c>
+      <c r="E369" s="95"/>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="95" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B370" s="95" t="s">
+        <v>4513</v>
+      </c>
+      <c r="C370" s="95" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D370" s="95" t="s">
+        <v>4513</v>
+      </c>
+      <c r="E370" s="95"/>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="95" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B371" s="95" t="s">
+        <v>4514</v>
+      </c>
+      <c r="C371" s="95" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D371" s="95" t="s">
+        <v>4514</v>
+      </c>
+      <c r="E371" s="95"/>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="95" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B372" s="95" t="s">
+        <v>4515</v>
+      </c>
+      <c r="C372" s="95" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D372" s="95" t="s">
+        <v>4515</v>
+      </c>
+      <c r="E372" s="95"/>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="95" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B373" s="95" t="s">
+        <v>4516</v>
+      </c>
+      <c r="C373" s="95" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D373" s="95" t="s">
+        <v>4516</v>
+      </c>
+      <c r="E373" s="95"/>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="95" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B374" s="95" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C374" s="95" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D374" s="95" t="s">
+        <v>4517</v>
+      </c>
+      <c r="E374" s="95"/>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="95" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B375" s="95" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C375" s="95" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D375" s="95" t="s">
+        <v>4518</v>
+      </c>
+      <c r="E375" s="95"/>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="95" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B376" s="95" t="s">
+        <v>4519</v>
+      </c>
+      <c r="C376" s="95" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D376" s="95" t="s">
+        <v>4519</v>
+      </c>
+      <c r="E376" s="95"/>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="95" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B377" s="95" t="s">
+        <v>4520</v>
+      </c>
+      <c r="C377" s="95" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D377" s="95" t="s">
+        <v>4520</v>
+      </c>
+      <c r="E377" s="95"/>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="97" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B378" s="95"/>
+      <c r="C378" s="95"/>
+      <c r="D378" s="95"/>
+      <c r="E378" s="95"/>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="95" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B379" s="95" t="s">
+        <v>4522</v>
+      </c>
+      <c r="C379" s="95" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D379" s="95" t="s">
+        <v>4522</v>
+      </c>
+      <c r="E379" s="95"/>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="95" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B380" s="95" t="s">
+        <v>4523</v>
+      </c>
+      <c r="C380" s="95" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D380" s="95" t="s">
+        <v>4523</v>
+      </c>
+      <c r="E380" s="95"/>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="95" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B381" s="95" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C381" s="95" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D381" s="95" t="s">
+        <v>4524</v>
+      </c>
+      <c r="E381" s="95"/>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="95" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B382" s="95" t="s">
+        <v>4525</v>
+      </c>
+      <c r="C382" s="95" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D382" s="95" t="s">
+        <v>4525</v>
+      </c>
+      <c r="E382" s="95"/>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="95" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B383" s="95" t="s">
+        <v>4526</v>
+      </c>
+      <c r="C383" s="95" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D383" s="95" t="s">
+        <v>4526</v>
+      </c>
+      <c r="E383" s="95"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="95" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B384" s="95" t="s">
+        <v>4527</v>
+      </c>
+      <c r="C384" s="95" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D384" s="95" t="s">
+        <v>4527</v>
+      </c>
+      <c r="E384" s="95"/>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="95" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B385" s="95" t="s">
+        <v>4528</v>
+      </c>
+      <c r="C385" s="95" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D385" s="95" t="s">
+        <v>4528</v>
+      </c>
+      <c r="E385" s="95"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="95" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B386" s="95" t="s">
+        <v>4529</v>
+      </c>
+      <c r="C386" s="95" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D386" s="95" t="s">
+        <v>4529</v>
+      </c>
+      <c r="E386" s="95"/>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="95" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B387" s="95" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C387" s="95" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D387" s="95" t="s">
+        <v>4530</v>
+      </c>
+      <c r="E387" s="95"/>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="95" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B388" s="95" t="s">
+        <v>4531</v>
+      </c>
+      <c r="C388" s="95" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D388" s="95" t="s">
+        <v>4531</v>
+      </c>
+      <c r="E388" s="95"/>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="95" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B389" s="95" t="s">
+        <v>4532</v>
+      </c>
+      <c r="C389" s="95" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D389" s="95" t="s">
+        <v>4532</v>
+      </c>
+      <c r="E389" s="95"/>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="95" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B390" s="95" t="s">
+        <v>4533</v>
+      </c>
+      <c r="C390" s="95" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D390" s="95" t="s">
+        <v>4533</v>
+      </c>
+      <c r="E390" s="95"/>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="95" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B391" s="95" t="s">
+        <v>4534</v>
+      </c>
+      <c r="C391" s="95" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D391" s="95" t="s">
+        <v>4534</v>
+      </c>
+      <c r="E391" s="95"/>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="95" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B392" s="95" t="s">
+        <v>4535</v>
+      </c>
+      <c r="C392" s="95" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D392" s="95" t="s">
+        <v>4535</v>
+      </c>
+      <c r="E392" s="95"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="95"/>
+      <c r="B393" s="95"/>
+      <c r="C393" s="95"/>
+      <c r="D393" s="95"/>
+      <c r="E393" s="95"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="94" t="s">
+        <v>4536</v>
+      </c>
+      <c r="B394" s="94"/>
+      <c r="C394" s="94"/>
+      <c r="D394" s="95"/>
+      <c r="E394" s="95"/>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="94" t="s">
+        <v>4537</v>
+      </c>
+      <c r="B395" s="94"/>
+      <c r="C395" s="95"/>
+      <c r="D395" s="95"/>
+      <c r="E395" s="95"/>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B396" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C396" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D396" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E396" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="95" t="s">
+        <v>460</v>
+      </c>
+      <c r="B397" s="95" t="s">
+        <v>4416</v>
+      </c>
+      <c r="C397" s="95" t="s">
+        <v>460</v>
+      </c>
+      <c r="D397" s="95" t="s">
+        <v>4416</v>
+      </c>
+      <c r="E397" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="95" t="s">
+        <v>462</v>
+      </c>
+      <c r="B398" s="95" t="s">
+        <v>4417</v>
+      </c>
+      <c r="C398" s="95" t="s">
+        <v>462</v>
+      </c>
+      <c r="D398" s="95" t="s">
+        <v>4417</v>
+      </c>
+      <c r="E398" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="B399" s="95" t="s">
+        <v>4418</v>
+      </c>
+      <c r="C399" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="D399" s="95" t="s">
+        <v>4418</v>
+      </c>
+      <c r="E399" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="95" t="s">
+        <v>466</v>
+      </c>
+      <c r="B400" s="95" t="s">
+        <v>4419</v>
+      </c>
+      <c r="C400" s="95" t="s">
+        <v>466</v>
+      </c>
+      <c r="D400" s="95" t="s">
+        <v>4419</v>
+      </c>
+      <c r="E400" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="94" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B401" s="94"/>
+      <c r="C401" s="95"/>
+      <c r="D401" s="95"/>
+      <c r="E401" s="95"/>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B402" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C402" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D402" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E402" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="95" t="s">
+        <v>728</v>
+      </c>
+      <c r="B403" s="95" t="s">
+        <v>4541</v>
+      </c>
+      <c r="C403" s="95" t="s">
+        <v>728</v>
+      </c>
+      <c r="D403" s="95" t="s">
+        <v>4541</v>
+      </c>
+      <c r="E403" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="B404" s="95" t="s">
+        <v>4542</v>
+      </c>
+      <c r="C404" s="95" t="s">
+        <v>733</v>
+      </c>
+      <c r="D404" s="95" t="s">
+        <v>4542</v>
+      </c>
+      <c r="E404" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="95" t="s">
+        <v>774</v>
+      </c>
+      <c r="B405" s="95" t="s">
+        <v>4461</v>
+      </c>
+      <c r="C405" s="95" t="s">
+        <v>774</v>
+      </c>
+      <c r="D405" s="95" t="s">
+        <v>4461</v>
+      </c>
+      <c r="E405" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="94" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B406" s="94"/>
+      <c r="C406" s="95"/>
+      <c r="D406" s="95"/>
+      <c r="E406" s="95"/>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B407" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C407" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D407" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E407" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="95" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B408" s="95" t="s">
+        <v>4544</v>
+      </c>
+      <c r="C408" s="95" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D408" s="95" t="s">
+        <v>4544</v>
+      </c>
+      <c r="E408" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="95" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B409" s="95" t="s">
+        <v>4545</v>
+      </c>
+      <c r="C409" s="95" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D409" s="95" t="s">
+        <v>4545</v>
+      </c>
+      <c r="E409" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="95" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B410" s="95" t="s">
+        <v>4546</v>
+      </c>
+      <c r="C410" s="95" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D410" s="95" t="s">
+        <v>4546</v>
+      </c>
+      <c r="E410" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="94" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B411" s="94"/>
+      <c r="C411" s="95"/>
+      <c r="D411" s="95"/>
+      <c r="E411" s="95"/>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B412" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C412" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D412" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E412" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="95" t="s">
+        <v>985</v>
+      </c>
+      <c r="B413" s="95" t="s">
+        <v>4548</v>
+      </c>
+      <c r="C413" s="95" t="s">
+        <v>985</v>
+      </c>
+      <c r="D413" s="95" t="s">
+        <v>4548</v>
+      </c>
+      <c r="E413" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="94" t="s">
+        <v>4549</v>
+      </c>
+      <c r="B414" s="95"/>
+      <c r="C414" s="95"/>
+      <c r="D414" s="95"/>
+      <c r="E414" s="95"/>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B415" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C415" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D415" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E415" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="B416" s="95" t="s">
+        <v>4550</v>
+      </c>
+      <c r="C416" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="D416" s="95" t="s">
+        <v>4550</v>
+      </c>
+      <c r="E416" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="95" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B417" s="95" t="s">
+        <v>4551</v>
+      </c>
+      <c r="C417" s="95" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D417" s="95" t="s">
+        <v>4551</v>
+      </c>
+      <c r="E417" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="95" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B418" s="95" t="s">
+        <v>4552</v>
+      </c>
+      <c r="C418" s="95" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D418" s="95" t="s">
+        <v>4552</v>
+      </c>
+      <c r="E418" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="94" t="s">
+        <v>4553</v>
+      </c>
+      <c r="B419" s="94"/>
+      <c r="C419" s="95"/>
+      <c r="D419" s="95"/>
+      <c r="E419" s="95"/>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B420" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C420" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D420" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E420" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="95" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B421" s="95" t="s">
+        <v>4554</v>
+      </c>
+      <c r="C421" s="95" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D421" s="95" t="s">
+        <v>4554</v>
+      </c>
+      <c r="E421" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="95" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B422" s="95" t="s">
+        <v>4555</v>
+      </c>
+      <c r="C422" s="95" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D422" s="95" t="s">
+        <v>4555</v>
+      </c>
+      <c r="E422" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="95" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B423" s="95" t="s">
+        <v>4556</v>
+      </c>
+      <c r="C423" s="95" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D423" s="95" t="s">
+        <v>4556</v>
+      </c>
+      <c r="E423" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="95" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B424" s="95" t="s">
+        <v>4557</v>
+      </c>
+      <c r="C424" s="95" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D424" s="95" t="s">
+        <v>4557</v>
+      </c>
+      <c r="E424" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="95" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B425" s="95" t="s">
+        <v>4558</v>
+      </c>
+      <c r="C425" s="95" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D425" s="95" t="s">
+        <v>4558</v>
+      </c>
+      <c r="E425" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="95" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B426" s="95" t="s">
+        <v>4559</v>
+      </c>
+      <c r="C426" s="95" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D426" s="95" t="s">
+        <v>4559</v>
+      </c>
+      <c r="E426" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="95" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B427" s="95" t="s">
+        <v>4560</v>
+      </c>
+      <c r="C427" s="95" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D427" s="95" t="s">
+        <v>4560</v>
+      </c>
+      <c r="E427" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="94" t="s">
+        <v>4561</v>
+      </c>
+      <c r="B428" s="94"/>
+      <c r="C428" s="95"/>
+      <c r="D428" s="95"/>
+      <c r="E428" s="95"/>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B429" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C429" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D429" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E429" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="B430" s="95" t="s">
+        <v>4256</v>
+      </c>
+      <c r="C430" s="95" t="s">
+        <v>302</v>
+      </c>
+      <c r="D430" s="95" t="s">
+        <v>4256</v>
+      </c>
+      <c r="E430" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="94" t="s">
+        <v>4562</v>
+      </c>
+      <c r="B431" s="94"/>
+      <c r="C431" s="95"/>
+      <c r="D431" s="95"/>
+      <c r="E431" s="95"/>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B432" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C432" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D432" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E432" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="B433" s="95" t="s">
+        <v>4563</v>
+      </c>
+      <c r="C433" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="D433" s="95" t="s">
+        <v>4563</v>
+      </c>
+      <c r="E433" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="95" t="s">
+        <v>767</v>
+      </c>
+      <c r="B434" s="95" t="s">
+        <v>4457</v>
+      </c>
+      <c r="C434" s="95" t="s">
+        <v>767</v>
+      </c>
+      <c r="D434" s="95" t="s">
+        <v>4457</v>
+      </c>
+      <c r="E434" s="95" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="94" t="s">
+        <v>4564</v>
+      </c>
+      <c r="B435" s="94"/>
+      <c r="C435" s="95"/>
+      <c r="D435" s="95"/>
+      <c r="E435" s="95"/>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B436" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C436" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D436" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E436" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="95" t="s">
+        <v>556</v>
+      </c>
+      <c r="B437" s="95" t="s">
+        <v>4565</v>
+      </c>
+      <c r="C437" s="95" t="s">
+        <v>556</v>
+      </c>
+      <c r="D437" s="95" t="s">
+        <v>4565</v>
+      </c>
+      <c r="E437" s="95" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="95"/>
+      <c r="B438" s="95"/>
+      <c r="C438" s="95"/>
+      <c r="D438" s="95"/>
+      <c r="E438" s="95"/>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="94" t="s">
+        <v>4567</v>
+      </c>
+      <c r="B439" s="94"/>
+      <c r="C439" s="94"/>
+      <c r="D439" s="95"/>
+      <c r="E439" s="95"/>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="96" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B440" s="97" t="s">
+        <v>4180</v>
+      </c>
+      <c r="C440" s="97" t="s">
+        <v>4181</v>
+      </c>
+      <c r="D440" s="97" t="s">
+        <v>4182</v>
+      </c>
+      <c r="E440" s="97" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="95" t="s">
+        <v>4568</v>
+      </c>
+      <c r="B441" s="98" t="s">
+        <v>4569</v>
+      </c>
+      <c r="C441" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D441" s="95" t="s">
+        <v>4202</v>
+      </c>
+      <c r="E441" s="95" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="95" t="s">
+        <v>852</v>
+      </c>
+      <c r="B442" s="95" t="s">
+        <v>4473</v>
+      </c>
+      <c r="C442" s="95" t="s">
+        <v>852</v>
+      </c>
+      <c r="D442" s="95" t="s">
+        <v>4473</v>
+      </c>
+      <c r="E442" s="95" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="95" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B443" s="95" t="s">
+        <v>4571</v>
+      </c>
+      <c r="C443" s="95" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D443" s="95" t="s">
+        <v>4571</v>
+      </c>
+      <c r="E443" s="95" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="95" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B444" s="95" t="s">
+        <v>4572</v>
+      </c>
+      <c r="C444" s="95" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D444" s="95" t="s">
+        <v>4572</v>
+      </c>
+      <c r="E444" s="95" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
@@ -72665,26 +80327,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff8bdcad-3542-4323-86bd-14c21c3f7aaf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3b1f95c1-b942-483f-a7ae-72e9206acbbe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086B9F041FBE43F4EA228A7DE33D25903" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa4aef5da86d373306697e89583560c8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ff8bdcad-3542-4323-86bd-14c21c3f7aaf" xmlns:ns3="3b1f95c1-b942-483f-a7ae-72e9206acbbe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43248e4aa2fde1fd955a4889b9983cb3" ns2:_="" ns3:_="">
     <xsd:import namespace="ff8bdcad-3542-4323-86bd-14c21c3f7aaf"/>
@@ -72927,26 +80569,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B31F0FC8-7F87-4C90-81D3-A471F8C31DF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ff8bdcad-3542-4323-86bd-14c21c3f7aaf"/>
-    <ds:schemaRef ds:uri="3b1f95c1-b942-483f-a7ae-72e9206acbbe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D5106B3-893A-4D01-91DA-87F1F5779BA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ff8bdcad-3542-4323-86bd-14c21c3f7aaf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3b1f95c1-b942-483f-a7ae-72e9206acbbe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F11E83-E146-4E44-93FE-87FAAAAE51B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -72963,4 +80606,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D5106B3-893A-4D01-91DA-87F1F5779BA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B31F0FC8-7F87-4C90-81D3-A471F8C31DF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ff8bdcad-3542-4323-86bd-14c21c3f7aaf"/>
+    <ds:schemaRef ds:uri="3b1f95c1-b942-483f-a7ae-72e9206acbbe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>